--- a/Computation/LaplaceEqu.xlsx
+++ b/Computation/LaplaceEqu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomke\My Drive\Programs\courses\resources\Computation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B131F-358B-4C82-B3D3-FAAF72D6C81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BF9163-31A4-4B1A-9FBB-772763331EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41130" yWindow="5970" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="3120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Startup" sheetId="2" r:id="rId1"/>
@@ -412,76 +412,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>99.504991077436145</c:v>
+                  <c:v>99.506101147438727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99.01423871722298</c:v>
+                  <c:v>99.016419031854099</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>98.53159387000089</c:v>
+                  <c:v>98.534789196420718</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>98.060132386549498</c:v>
+                  <c:v>98.064273154364471</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>97.601849679480623</c:v>
+                  <c:v>97.6068532308702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>97.157430879161083</c:v>
+                  <c:v>97.163202885582564</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>96.72609010611319</c:v>
+                  <c:v>96.732526136025641</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>96.305455909173332</c:v>
+                  <c:v>96.312443128957028</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>95.891466334584251</c:v>
+                  <c:v>95.898885322296195</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>95.478225608475356</c:v>
+                  <c:v>95.485952257386487</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>95.057761717092234</c:v>
+                  <c:v>95.065669203237746</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>94.619604373060994</c:v>
+                  <c:v>94.627565158466439</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>94.150066250985418</c:v>
+                  <c:v>94.157954091983783</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>93.631039626315726</c:v>
+                  <c:v>93.638731554620861</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>93.037981318081336</c:v>
+                  <c:v>93.045359561193791</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>92.336476921419603</c:v>
+                  <c:v>92.343430728653914</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91.476178354857424</c:v>
+                  <c:v>91.482605695897817</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>90.379567439124131</c:v>
+                  <c:v>90.385376543601353</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>88.919762284427634</c:v>
+                  <c:v>88.924872993575306</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>86.873123028675735</c:v>
+                  <c:v>86.877467933630442</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>83.808296442307721</c:v>
+                  <c:v>83.81182178797377</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>78.798240756345962</c:v>
+                  <c:v>78.80090709481729</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>69.587095732669326</c:v>
+                  <c:v>69.588878315812366</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49.910031958259985</c:v>
+                  <c:v>49.910920865011207</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -552,76 +552,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>99.005724669931354</c:v>
+                  <c:v>99.007892337956008</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>98.020368341172968</c:v>
+                  <c:v>98.024625843850046</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>97.052002177174188</c:v>
+                  <c:v>97.058241586206222</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96.107083226693248</c:v>
+                  <c:v>96.115168612613303</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>95.189832166981162</c:v>
+                  <c:v>95.199602045249961</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>94.30177999327482</c:v>
+                  <c:v>94.3130500957935</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>93.44146951423113</c:v>
+                  <c:v>93.454035855580713</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>92.604262763002623</c:v>
+                  <c:v>92.617904966307037</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>91.782179152921202</c:v>
+                  <c:v>91.796663995306076</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>90.963669558071814</c:v>
+                  <c:v>90.978754690470709</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>90.133211985461116</c:v>
+                  <c:v>90.148649776277935</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>89.270584624262966</c:v>
+                  <c:v>89.286126071450411</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>88.349616183108495</c:v>
+                  <c:v>88.365014834907896</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>87.336106267284634</c:v>
+                  <c:v>87.351122088530843</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>86.184404278337681</c:v>
+                  <c:v>86.198807397180147</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>84.831743854260139</c:v>
+                  <c:v>84.845318123654181</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>83.188665247376278</c:v>
+                  <c:v>83.201211556959748</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>81.122325705148029</c:v>
+                  <c:v>81.133664982252824</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>78.426355702368539</c:v>
+                  <c:v>78.436331545946402</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>74.764430902070387</c:v>
+                  <c:v>74.772911800160045</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>69.561820008715884</c:v>
+                  <c:v>69.568701098568923</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>61.797569405438928</c:v>
+                  <c:v>61.802773745290516</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>49.640109312981565</c:v>
+                  <c:v>49.643588645362698</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>30.053031741751788</c:v>
+                  <c:v>30.054766739798566</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -692,76 +692,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98.49753769133622</c:v>
+                  <c:v>98.500683437493734</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>97.009505169187932</c:v>
+                  <c:v>97.015683591986601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95.548959642334609</c:v>
+                  <c:v>95.558013988676421</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>94.126361628632054</c:v>
+                  <c:v>94.138094507281949</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>92.748610393242217</c:v>
+                  <c:v>92.762787332118279</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>91.418381311896837</c:v>
+                  <c:v>91.434734787701288</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90.133738479527821</c:v>
+                  <c:v>90.151972374740581</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.887939265187697</c:v>
+                  <c:v>88.907733701053033</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>87.669310373970518</c:v>
+                  <c:v>87.690326860999221</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>86.461053658934659</c:v>
+                  <c:v>86.482940498931256</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>85.240824099722758</c:v>
+                  <c:v>85.26322196582133</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>83.979898023847312</c:v>
+                  <c:v>84.00244563795593</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>82.6416997938679</c:v>
+                  <c:v>82.664039614768114</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>81.179357440510643</c:v>
+                  <c:v>81.201141271119269</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>79.531778501080581</c:v>
+                  <c:v>79.552672920508158</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>77.617422270332355</c:v>
+                  <c:v>77.637113795746345</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>75.324406943902062</c:v>
+                  <c:v>75.342606829110395</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>72.494708952822421</c:v>
+                  <c:v>72.511157535096515</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>68.898899163507025</c:v>
+                  <c:v>68.913369677492469</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>64.196420897990293</c:v>
+                  <c:v>64.208722685493186</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>57.876980143929707</c:v>
+                  <c:v>57.88696120066291</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>49.190105263621582</c:v>
+                  <c:v>49.197654078268037</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>37.122738970404136</c:v>
+                  <c:v>37.12778562711766</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>20.661985175756151</c:v>
+                  <c:v>20.66450170790992</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -832,76 +832,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.974918765651353</c:v>
+                  <c:v>97.978938554240187</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>95.971151413640612</c:v>
+                  <c:v>95.979046331498083</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>94.00796466534365</c:v>
+                  <c:v>94.019534222886492</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>92.100787088694375</c:v>
+                  <c:v>92.115778867045918</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90.259859190632056</c:v>
+                  <c:v>90.277973397208399</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>88.489388133579013</c:v>
+                  <c:v>88.510282761263582</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>86.787154756158841</c:v>
+                  <c:v>86.810451288030009</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>85.144435711111967</c:v>
+                  <c:v>85.169725304540265</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>83.546059190355095</c:v>
+                  <c:v>83.572909265255689</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>81.970400051506743</c:v>
+                  <c:v>81.998361198012901</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>80.389122026983557</c:v>
+                  <c:v>80.417735138296536</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>78.766472894136626</c:v>
+                  <c:v>78.795276421381828</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>77.057917032345514</c:v>
+                  <c:v>77.086454250538665</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>75.207835052827136</c:v>
+                  <c:v>75.235661221139281</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>73.145920368849261</c:v>
+                  <c:v>73.172609664823597</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>70.781750777373333</c:v>
+                  <c:v>70.806902884067284</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>67.996823069732358</c:v>
+                  <c:v>68.020069297294924</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>64.63319664571813</c:v>
+                  <c:v>64.654205474865336</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>60.478104726838986</c:v>
+                  <c:v>60.496586671093581</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>55.245368066672498</c:v>
+                  <c:v>55.261079762938245</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>48.559570208727777</c:v>
+                  <c:v>48.572317661450711</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>39.963129499168083</c:v>
+                  <c:v>39.972770421512934</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>28.998754277681023</c:v>
+                  <c:v>29.005199493205296</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>15.472169327015765</c:v>
+                  <c:v>15.475383216542127</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -972,76 +972,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.430983277458779</c:v>
+                  <c:v>97.435751678373947</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.892212626750648</c:v>
+                  <c:v>94.901577599876745</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>92.410954448614461</c:v>
+                  <c:v>92.424677929450311</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90.00895529210699</c:v>
+                  <c:v>90.026737619329452</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>87.700642210405007</c:v>
+                  <c:v>87.722127541916421</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85.492147150013523</c:v>
+                  <c:v>85.516929594884829</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>83.381045570390057</c:v>
+                  <c:v>83.408675967197382</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81.356577694737453</c:v>
+                  <c:v>81.386570957148663</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>79.400078083763418</c:v>
+                  <c:v>79.431921023580784</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>77.485352395641343</c:v>
+                  <c:v>77.518511922310807</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>75.578777947106886</c:v>
+                  <c:v>75.61270953154974</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>73.63894140657402</c:v>
+                  <c:v>73.67309768675824</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>71.615647535487014</c:v>
+                  <c:v>71.649486932153522</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>69.448132947276378</c:v>
+                  <c:v>69.481128151386159</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>67.062305338542743</c:v>
+                  <c:v>67.093951527975449</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>64.366826384100762</c:v>
+                  <c:v>64.39664902647327</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>61.247927840801758</c:v>
+                  <c:v>61.275489942399801</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>57.563140845736086</c:v>
+                  <c:v>57.58804951369757</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>53.13494724517156</c:v>
+                  <c:v>53.156859441258469</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>47.747369944956034</c:v>
+                  <c:v>47.765997324326406</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>41.152798009256529</c:v>
+                  <c:v>41.167910756212862</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>33.104084554076863</c:v>
+                  <c:v>33.115514148255158</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23.436977072454638</c:v>
+                  <c:v>23.444617942601525</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12.227937067999104</c:v>
+                  <c:v>12.23174711552635</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1117,76 +1117,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96.856798601422923</c:v>
+                  <c:v>96.862172428043706</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93.755756238254804</c:v>
+                  <c:v>93.766309968386736</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.734678191905061</c:v>
+                  <c:v>90.750143250183214</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>87.823428663796989</c:v>
+                  <c:v>87.843467063896185</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85.04159688823367</c:v>
+                  <c:v>85.065807350412683</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>82.397500997011747</c:v>
+                  <c:v>82.425425872238861</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>79.888289836941709</c:v>
+                  <c:v>79.919422758538431</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77.500737641522818</c:v>
+                  <c:v>77.53453181442643</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>75.212308590034553</c:v>
+                  <c:v>75.248185615848996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>72.992138585926995</c:v>
+                  <c:v>73.029497709424305</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>70.801680839027227</c:v>
+                  <c:v>70.839908489333965</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>68.594852165472361</c:v>
+                  <c:v>68.633331653579262</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>66.3175839440663</c:v>
+                  <c:v>66.355705168337948</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>63.906729549929231</c:v>
+                  <c:v>63.943898553758324</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>61.288328055243653</c:v>
+                  <c:v>61.323976276625793</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>58.375308893052335</c:v>
+                  <c:v>58.408901945271545</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>55.064909468939454</c:v>
+                  <c:v>55.095955295206018</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>51.23648130734334</c:v>
+                  <c:v>51.264537560371764</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46.751164505829571</c:v>
+                  <c:v>46.775845016014472</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>41.456358999077601</c:v>
+                  <c:v>41.477339211917332</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>35.200161452477673</c:v>
+                  <c:v>35.217182736777204</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>27.863429399976358</c:v>
+                  <c:v>27.876302152493437</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>19.417129827375085</c:v>
+                  <c:v>19.425735326146981</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10.002600987071055</c:v>
+                  <c:v>10.00689197373617</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1262,76 +1262,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96.240451431901022</c:v>
+                  <c:v>96.246273808444414</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92.53932985651231</c:v>
+                  <c:v>92.550764184908985</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88.948565658879829</c:v>
+                  <c:v>88.965320625558547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>85.50847460971741</c:v>
+                  <c:v>85.530183705663788</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>82.244804286375967</c:v>
+                  <c:v>82.271032450438668</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>79.167957211357276</c:v>
+                  <c:v>79.198208347160545</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>76.273860966198143</c:v>
+                  <c:v>76.307586246207705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.545759250549935</c:v>
+                  <c:v>73.582366109130774</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>70.956264094571935</c:v>
+                  <c:v>70.995125799027861</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>68.46919607115727</c:v>
+                  <c:v>68.509661746310485</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>66.040937985331098</c:v>
+                  <c:v>66.082342953889338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>63.621185842363793</c:v>
+                  <c:v>63.662862130939843</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>61.153090198390423</c:v>
+                  <c:v>61.194377048443329</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>58.572857479138797</c:v>
+                  <c:v>58.613111694145886</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>55.808953454529444</c:v>
+                  <c:v>55.847559410158155</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52.781157686696673</c:v>
+                  <c:v>52.817536830281867</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>49.399907063126896</c:v>
+                  <c:v>49.433526732856159</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45.566699018141207</c:v>
+                  <c:v>45.597080421276182</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>41.176860611171669</c:v>
+                  <c:v>41.203585814414645</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>36.126731884883306</c:v>
+                  <c:v>36.149449688412659</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>30.328052939457454</c:v>
+                  <c:v>30.346483528735803</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23.732337114038724</c:v>
+                  <c:v>23.746275409555679</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>16.365509042626861</c:v>
+                  <c:v>16.374826696403069</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.365336094738149</c:v>
+                  <c:v>8.3699821126830862</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1407,76 +1407,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>95.565673570560463</c:v>
+                  <c:v>95.571778328083099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91.212540038738979</c:v>
+                  <c:v>91.224528586930859</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>87.011771705664884</c:v>
+                  <c:v>87.029338261151608</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>83.017089522041701</c:v>
+                  <c:v>83.039849469919176</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>79.261176297956894</c:v>
+                  <c:v>79.288673173170764</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.755648857100624</c:v>
+                  <c:v>75.787362241443304</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72.493422476888099</c:v>
+                  <c:v>72.528776720145856</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>69.452158126595833</c:v>
+                  <c:v>69.490531788137673</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>66.597775486382176</c:v>
+                  <c:v>66.638511380092751</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>63.887426115927482</c:v>
+                  <c:v>63.929841827428326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>61.271671449474219</c:v>
+                  <c:v>61.315070180782584</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>58.695845328393695</c:v>
+                  <c:v>58.739526912374565</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56.100716160601792</c:v>
+                  <c:v>56.14398807666349</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>53.422639936803307</c:v>
+                  <c:v>53.464828151150634</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.593454661660466</c:v>
+                  <c:v>50.633914110858463</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>47.540446474660691</c:v>
+                  <c:v>47.578571010954626</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44.186848501854854</c:v>
+                  <c:v>44.222080123132649</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>40.453534984473663</c:v>
+                  <c:v>40.485372181218601</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>36.262836558604008</c:v>
+                  <c:v>36.290841624690138</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>31.545646271607641</c:v>
+                  <c:v>31.569451445101741</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>26.252974446585604</c:v>
+                  <c:v>26.27228677034865</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>20.372352140653962</c:v>
+                  <c:v>20.386956959764351</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>13.947230163616174</c:v>
+                  <c:v>13.95699320656078</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.093233345888736</c:v>
+                  <c:v>7.0981013680406084</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1552,76 +1552,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94.809698976866784</c:v>
+                  <c:v>94.81591526459512</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.733378754449063</c:v>
+                  <c:v>89.745585984530251</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84.868883052790864</c:v>
+                  <c:v>84.886769509427026</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.286924825423938</c:v>
+                  <c:v>80.310098532330102</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.027149990023048</c:v>
+                  <c:v>76.055145835394939</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>72.100025256454799</c:v>
+                  <c:v>72.132313049905861</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>68.49200638071764</c:v>
+                  <c:v>68.527999748218051</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>65.171658599028888</c:v>
+                  <c:v>65.210724609451972</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>62.095236084576158</c:v>
+                  <c:v>62.136705487907527</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>59.211043395708664</c:v>
+                  <c:v>59.254221338886758</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>56.462458065484462</c:v>
+                  <c:v>56.506635137957943</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>53.789789609437086</c:v>
+                  <c:v>53.834253057687377</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>51.131271263947369</c:v>
+                  <c:v>51.175316203327235</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>48.423514142117199</c:v>
+                  <c:v>48.466454586281486</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>45.601762347003756</c:v>
+                  <c:v>45.642941870765036</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>42.600309724493016</c:v>
+                  <c:v>42.639111575800939</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>39.353491488012494</c:v>
+                  <c:v>39.389347969422836</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35.797743380525979</c:v>
+                  <c:v>35.830144330263138</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>31.875293570391158</c:v>
+                  <c:v>31.903793787932415</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>27.540033215263804</c:v>
+                  <c:v>27.56425869604125</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22.765839371490596</c:v>
+                  <c:v>22.785492239320579</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17.556861763152913</c:v>
+                  <c:v>17.571723816636453</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11.957823075191346</c:v>
+                  <c:v>11.967757894667162</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.0603661047990114</c:v>
+                  <c:v>6.0653196984186755</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1697,76 +1697,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93.939739718919341</c:v>
+                  <c:v>93.945896707410441</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.042386646475208</c:v>
+                  <c:v>88.054477098111448</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.443448334598443</c:v>
+                  <c:v>82.461163172749053</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.234566041716704</c:v>
+                  <c:v>77.257516705306855</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>72.460460994173246</c:v>
+                  <c:v>72.488186510323047</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.125281559227901</c:v>
+                  <c:v>68.15725653861719</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>64.202903558248423</c:v>
+                  <c:v>64.238547019324528</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>60.647217053994417</c:v>
+                  <c:v>60.685901969867629</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>57.400449276164196</c:v>
+                  <c:v>57.44151272469778</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>54.399035199137622</c:v>
+                  <c:v>54.441788982911305</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.577309449160602</c:v>
+                  <c:v>51.621051038395841</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>48.869565474994289</c:v>
+                  <c:v>48.91358911400178</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46.211047178487057</c:v>
+                  <c:v>46.254654985605569</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>43.538365670429023</c:v>
+                  <c:v>43.580878553632544</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40.789754383846201</c:v>
+                  <c:v>40.830522589991588</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>37.905523227012139</c:v>
+                  <c:v>37.94393634274077</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>34.829050316075282</c:v>
+                  <c:v>34.864546543147029</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>31.50864097427969</c:v>
+                  <c:v>31.540715511862359</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>27.900550310285261</c:v>
+                  <c:v>27.92876269145879</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>23.973344652609217</c:v>
+                  <c:v>23.997324901826929</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.71348099029953</c:v>
+                  <c:v>19.732934492287185</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>15.131427388843214</c:v>
+                  <c:v>15.146138386695471</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>10.266831224084838</c:v>
+                  <c:v>10.27666489423801</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.1904069886959228</c:v>
+                  <c:v>5.1953100719810354</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1842,76 +1842,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>92.906869465311161</c:v>
+                  <c:v>92.912801011094786</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>86.05297361141389</c:v>
+                  <c:v>86.064621059671381</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>79.627949199252669</c:v>
+                  <c:v>79.645014482168108</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73.747419562640914</c:v>
+                  <c:v>73.769528046830573</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>68.454834091989497</c:v>
+                  <c:v>68.481541406880993</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63.737722523280574</c:v>
+                  <c:v>63.768522278138178</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>59.547093976305867</c:v>
+                  <c:v>59.581426274683011</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>55.813840430746716</c:v>
+                  <c:v>55.851101079358976</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>52.460291606427745</c:v>
+                  <c:v>52.499841902667981</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>49.407320993284749</c:v>
+                  <c:v>49.448497962399955</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46.578161142157292</c:v>
+                  <c:v>46.620288082165771</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>43.900097801930016</c:v>
+                  <c:v>43.94249498246559</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41.304968777082827</c:v>
+                  <c:v>41.346964128341604</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38.729130051574032</c:v>
+                  <c:v>38.770069672227194</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>36.113350220184039</c:v>
+                  <c:v>36.152608529254834</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>33.402963502090749</c:v>
+                  <c:v>33.439952859998769</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>30.548531894808594</c:v>
+                  <c:v>30.582711523508301</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>27.507207698547163</c:v>
+                  <c:v>27.538091740170358</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>24.244911500426163</c:v>
+                  <c:v>24.272076068083816</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20.739305329825918</c:v>
+                  <c:v>20.76239442299681</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>16.983305661840397</c:v>
+                  <c:v>17.002035841598882</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12.988530637788415</c:v>
+                  <c:v>13.002694383316669</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.7876644859023969</c:v>
+                  <c:v>8.7971321824336819</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.4344296545812103</c:v>
+                  <c:v>4.4391501931419297</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1992,76 +1992,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>91.634760921390296</c:v>
+                  <c:v>91.640310060086222</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>83.634683268691177</c:v>
+                  <c:v>83.645579541928782</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>76.267947306526167</c:v>
+                  <c:v>76.283911592533926</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.672318990612936</c:v>
+                  <c:v>69.693000544048132</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.87372161337224</c:v>
+                  <c:v>63.898704466806699</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>58.823667264503705</c:v>
+                  <c:v>58.852477461057688</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>54.433894905407158</c:v>
+                  <c:v>54.46600847647796</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50.600743567509355</c:v>
+                  <c:v>50.635595158545328</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>47.219539441536448</c:v>
+                  <c:v>47.256531476931499</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>44.191779248520319</c:v>
+                  <c:v>44.23029151446228</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>41.427899328670328</c:v>
+                  <c:v>41.467298840810415</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38.847678871010856</c:v>
+                  <c:v>38.887329882859767</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>36.379583452116805</c:v>
+                  <c:v>36.418857450883522</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>33.959819487093036</c:v>
+                  <c:v>33.998105017021018</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>31.531537704450173</c:v>
+                  <c:v>31.5682498542599</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>29.044434462419744</c:v>
+                  <c:v>29.07902385380936</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>26.454893094504467</c:v>
+                  <c:v>26.486854213201916</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>23.726734869935061</c:v>
+                  <c:v>23.755613589752606</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.832572672931633</c:v>
+                  <c:v>20.857972836645772</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17.755651202453752</c:v>
+                  <c:v>17.777240140896687</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>14.491899169953959</c:v>
+                  <c:v>14.509412062014773</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>11.051720341859664</c:v>
+                  <c:v>11.064963342517782</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.4608636351362545</c:v>
+                  <c:v>7.4697157253874593</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.7596462360160139</c:v>
+                  <c:v>3.764059776687148</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2142,76 +2142,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.997487613557524</c:v>
+                  <c:v>90.002510750638208</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>80.583045822633224</c:v>
+                  <c:v>80.592909024263349</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>72.136830409435746</c:v>
+                  <c:v>72.151280787125003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>64.800178333779726</c:v>
+                  <c:v>64.818898167427719</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>58.544055354254454</c:v>
+                  <c:v>58.566667898446006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>53.249317861199863</c:v>
+                  <c:v>53.275393903756481</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>48.764061476988005</c:v>
+                  <c:v>48.793126571239384</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44.935685209356464</c:v>
+                  <c:v>44.967227491670251</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.625328358776436</c:v>
+                  <c:v>41.658806852198929</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38.712341794296492</c:v>
+                  <c:v>38.747195088173129</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>36.093962417588905</c:v>
+                  <c:v>36.129617602326057</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>33.683119316811094</c:v>
+                  <c:v>33.71900104316363</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>31.405851383501755</c:v>
+                  <c:v>31.441390907609158</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29.199011979183929</c:v>
+                  <c:v>29.233656048706607</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>27.008532636464057</c:v>
+                  <c:v>27.041752070203614</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>24.788330490574623</c:v>
+                  <c:v>24.819628304405768</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>22.499859231191678</c:v>
+                  <c:v>22.528778167352591</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>20.112255395457339</c:v>
+                  <c:v>20.138384720429592</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17.602983941000073</c:v>
+                  <c:v>17.625965389352828</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>14.958820012990772</c:v>
+                  <c:v>14.978352770463001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12.176913489910101</c:v>
+                  <c:v>12.192758128259186</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9.2655836400967466</c:v>
+                  <c:v>9.2775649382796495</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.2444209225513472</c:v>
+                  <c:v>6.2524295329074642</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.1432908334811116</c:v>
+                  <c:v>3.1472837769331754</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2292,76 +2292,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.772140728371028</c:v>
+                  <c:v>87.776511404075464</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.563177176155946</c:v>
+                  <c:v>76.571759068683974</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.896143626460429</c:v>
+                  <c:v>66.908716520209722</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.847500446682467</c:v>
+                  <c:v>58.863787715365135</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.252994050533125</c:v>
+                  <c:v>52.272667718923998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.865476547628042</c:v>
+                  <c:v>46.888163007846792</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42.437336083649917</c:v>
+                  <c:v>42.462622397092474</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38.752594747529095</c:v>
+                  <c:v>38.780035454950628</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>35.633733682346701</c:v>
+                  <c:v>35.66285803535586</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>32.938283446228198</c:v>
+                  <c:v>32.968602963977645</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.552475349948377</c:v>
+                  <c:v>30.583491595597032</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>28.384970761850859</c:v>
+                  <c:v>28.416183224989812</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>26.36167721634077</c:v>
+                  <c:v>26.392591180607056</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>24.421831311482535</c:v>
+                  <c:v>24.451965581611852</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>22.51523794058275</c:v>
+                  <c:v>22.544132300698031</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>20.600484049381258</c:v>
+                  <c:v>20.627706324814028</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18.643947373496815</c:v>
+                  <c:v>18.669099972200904</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.619434125547198</c:v>
+                  <c:v>16.642159942349423</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14.508279548242701</c:v>
+                  <c:v>14.528267125774327</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>12.299724664446876</c:v>
+                  <c:v>12.316712518433324</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9913458392771961</c:v>
+                  <c:v>10.005125872585168</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.5892760176431544</c:v>
+                  <c:v>7.5996959665982819</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.107943329206373</c:v>
+                  <c:v>5.1149082065813456</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.5690954617226129</c:v>
+                  <c:v>2.5725679827470103</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2442,76 +2442,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>84.527895571282613</c:v>
+                  <c:v>84.531507688661193</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>71.001374412635457</c:v>
+                  <c:v>71.008466746973056</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60.037060895115033</c:v>
+                  <c:v>60.047451324471581</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>51.440678852589926</c:v>
+                  <c:v>51.454138632304243</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44.754935722891062</c:v>
+                  <c:v>44.771193676384407</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>39.522249010776335</c:v>
+                  <c:v>39.540996261359389</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35.367201491329972</c:v>
+                  <c:v>35.388096677635801</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>32.003613234135784</c:v>
+                  <c:v>32.026288144701468</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29.218716871347439</c:v>
+                  <c:v>29.242782426272132</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>26.854571316859197</c:v>
+                  <c:v>26.879623816703393</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>24.792672986864563</c:v>
+                  <c:v>24.818300541430126</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22.942599419621324</c:v>
+                  <c:v>22.968388462423455</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.234043890101219</c:v>
+                  <c:v>21.259585678693412</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19.611386993839123</c:v>
+                  <c:v>19.636283992151149</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>18.030093217553794</c:v>
+                  <c:v>18.053965254478374</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16.454410567555595</c:v>
+                  <c:v>16.476900666524006</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>14.856003123648092</c:v>
+                  <c:v>14.876782901118158</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13.213246204322679</c:v>
+                  <c:v>13.232020741091858</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>11.510968569231121</c:v>
+                  <c:v>11.527480667272975</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.7404475374958857</c:v>
+                  <c:v>9.75448128645046</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7.8994647030774754</c:v>
+                  <c:v>7.9108482943193712</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.9922280616557595</c:v>
+                  <c:v>6.000835803610542</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.028979019126524</c:v>
+                  <c:v>4.034732524698831</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.0251470948431254</c:v>
+                  <c:v>2.0280156298778214</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2592,76 +2592,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79.338065080963617</c:v>
+                  <c:v>79.340835503258162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.877360697974972</c:v>
+                  <c:v>62.882800304829047</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50.810042210623308</c:v>
+                  <c:v>50.818011236552849</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.123212794771625</c:v>
+                  <c:v>42.133535711761013</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35.80381446422404</c:v>
+                  <c:v>35.816283201447135</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.101374928249992</c:v>
+                  <c:v>31.115752506846224</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>27.5055995777244</c:v>
+                  <c:v>27.521624116283196</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.67593120305196</c:v>
+                  <c:v>24.693320244026836</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22.382940212121206</c:v>
+                  <c:v>22.40139531360213</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.468602657424722</c:v>
+                  <c:v>20.487814188793379</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18.821036441752238</c:v>
+                  <c:v>18.840688516037645</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>17.358700657160391</c:v>
+                  <c:v>17.378476127750179</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16.020502731539128</c:v>
+                  <c:v>16.040088176649263</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14.759570681249926</c:v>
+                  <c:v>14.778661296568698</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.539328949911173</c:v>
+                  <c:v>13.557633268434934</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.3310540404877</c:v>
+                  <c:v>12.348298399020949</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.112401200047337</c:v>
+                  <c:v>11.128333874336185</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.8665726372661968</c:v>
+                  <c:v>9.8809675723657797</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.5818954959599001</c:v>
+                  <c:v>8.5945555651937831</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.2516276606785492</c:v>
+                  <c:v>7.2623873953157103</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.8738338111480379</c:v>
+                  <c:v>5.8825615534821543</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.4511899686636749</c:v>
+                  <c:v>4.457789413219615</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.9905960952649764</c:v>
+                  <c:v>2.9950071959919797</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.5025134467491084</c:v>
+                  <c:v>1.5047126818478915</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2742,76 +2742,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>69.947002526199483</c:v>
+                  <c:v>69.948872971016058</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.359958654651777</c:v>
+                  <c:v>50.363631156406115</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.202531174582973</c:v>
+                  <c:v>38.20791132641547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.438311594262338</c:v>
+                  <c:v>30.445280840371026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25.235729656668301</c:v>
+                  <c:v>25.244147469548295</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21.573831298673653</c:v>
+                  <c:v>21.58353763670338</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.877884816645189</c:v>
+                  <c:v>18.888702831853067</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.811565509787947</c:v>
+                  <c:v>16.823304471973962</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.168503538789611</c:v>
+                  <c:v>15.180961938286632</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.815855891455188</c:v>
+                  <c:v>13.828824678861533</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12.66416261883097</c:v>
+                  <c:v>12.677428536235173</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.650657219087133</c:v>
+                  <c:v>11.664006173870046</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.72968901758081</c:v>
+                  <c:v>10.742909447062479</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.8670576082883663</c:v>
+                  <c:v>9.8799437815243198</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.0365917537026696</c:v>
+                  <c:v>9.0489469558411741</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.2180697613670013</c:v>
+                  <c:v>8.2297093063309479</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.3959698195496539</c:v>
+                  <c:v>7.4067238385280634</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.558743043943644</c:v>
+                  <c:v>6.5684590003296215</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.6984091463933275</c:v>
+                  <c:v>5.7069540323798673</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.8103305111764803</c:v>
+                  <c:v>4.8175926871401584</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.8930503456059089</c:v>
+                  <c:v>3.898940990524177</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.9481000853029871</c:v>
+                  <c:v>2.9525542345548561</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.9797008831906977</c:v>
+                  <c:v>1.9826780389242262</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.99431029199712817</c:v>
+                  <c:v>0.99579460051490887</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -2887,76 +2887,76 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50.089985405518846</c:v>
+                  <c:v>50.09092358752828</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.412938710970952</c:v>
+                  <c:v>30.414780759950428</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21.201810220087264</c:v>
+                  <c:v>21.204508766253443</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.191770265132639</c:v>
+                  <c:v>16.195265823356426</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.126958365504287</c:v>
+                  <c:v>13.131180428988982</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.080332525599584</c:v>
+                  <c:v>11.085200800260612</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.6205393084776389</c:v>
+                  <c:v>9.6259650727813035</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.5239386670173261</c:v>
+                  <c:v>8.5298262402044784</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.6636485515287198</c:v>
+                  <c:v>7.6698968512084473</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.9621506503871826</c:v>
+                  <c:v>6.9686548185187807</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.3690967793202269</c:v>
+                  <c:v>6.3757498537111355</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.8500724617992574</c:v>
+                  <c:v>5.8567670685475033</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.380534477445007</c:v>
+                  <c:v>5.3871645183675199</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.9423750952077627</c:v>
+                  <c:v>4.9488374033377207</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.521907016268802</c:v>
+                  <c:v>4.5281029520821336</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.1086600125915664</c:v>
+                  <c:v>4.1144969738211872</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.6946621617180462</c:v>
+                  <c:v>3.7000549804952882</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.2740178117592476</c:v>
+                  <c:v>3.2788900144148667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.8426651598947483</c:v>
+                  <c:v>2.846950067052306</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.3982329326901097</c:v>
+                  <c:v>2.4018745802527537</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.9399354526230106</c:v>
+                  <c:v>1.9428893178171331</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.4684580733081234</c:v>
+                  <c:v>1.4706915940000735</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.98579644863688187</c:v>
+                  <c:v>0.98728932855295437</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.49502668515850251</c:v>
+                  <c:v>0.49577098226696581</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4148,8 +4148,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.109335238041395E-2"/>
-          <c:y val="9.4690860552795394E-2"/>
+          <c:x val="1.7656473219299435E-2"/>
+          <c:y val="9.4690932175638995E-2"/>
           <c:w val="0.90344363625395929"/>
           <c:h val="0.78768367294631558"/>
         </c:manualLayout>
@@ -4281,76 +4281,76 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50.456859446151313</c:v>
+                  <c:v>50.456764197585272</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.683146501104147</c:v>
+                  <c:v>70.682969605101235</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80.447400174078865</c:v>
+                  <c:v>80.447161086211608</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86.013960449990762</c:v>
+                  <c:v>86.013682229156558</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89.634835999829193</c:v>
+                  <c:v>89.63454276532633</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>92.228011909717864</c:v>
+                  <c:v>92.227726242672489</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>94.208305341087708</c:v>
+                  <c:v>94.208045871548535</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>95.773257233592403</c:v>
+                  <c:v>95.773036680365792</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>97.014230056566987</c:v>
+                  <c:v>97.014054068241336</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>97.97034288368215</c:v>
+                  <c:v>97.970210164352636</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>98.667603215408903</c:v>
+                  <c:v>98.667507403164365</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>99.149160551240612</c:v>
+                  <c:v>99.149093489752943</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>99.46759824152744</c:v>
+                  <c:v>99.467552271873245</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99.671590676709656</c:v>
+                  <c:v>99.671559592545336</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99.799401877007853</c:v>
+                  <c:v>99.799381043258833</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99.87828145729857</c:v>
+                  <c:v>99.878267574641924</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99.926474636469123</c:v>
+                  <c:v>99.926465423672141</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99.955727726058754</c:v>
+                  <c:v>99.955721633973099</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99.973415484353808</c:v>
+                  <c:v>99.973411473222185</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99.984095306564967</c:v>
+                  <c:v>99.984092684567273</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.990557971545314</c:v>
+                  <c:v>99.990556282340151</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99.994507724042549</c:v>
+                  <c:v>99.994506670402046</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.996992333953088</c:v>
+                  <c:v>99.996991726946703</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.998673478978887</c:v>
+                  <c:v>99.998673204954059</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>100</c:v>
@@ -4385,76 +4385,76 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.144268646697213</c:v>
+                  <c:v>31.144087185239417</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.828289995930547</c:v>
+                  <c:v>51.827953136607391</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65.092447421366714</c:v>
+                  <c:v>65.091992510587829</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73.973553693887169</c:v>
+                  <c:v>73.973025065087285</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80.297318466040764</c:v>
+                  <c:v>80.296762589475307</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85.068855821649635</c:v>
+                  <c:v>85.068316333814153</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>88.83190753198835</c:v>
+                  <c:v>88.831420563155064</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>91.870456552630728</c:v>
+                  <c:v>91.870046781672613</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>94.313291415717316</c:v>
+                  <c:v>94.312969428246419</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.199517213172413</c:v>
+                  <c:v>96.199279186004475</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>97.55089458101358</c:v>
+                  <c:v>97.55072595855161</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>98.461430541621056</c:v>
+                  <c:v>98.461314283974019</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>99.049634832758684</c:v>
+                  <c:v>99.049556005194532</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99.419357962652597</c:v>
+                  <c:v>99.419305055049193</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99.647732294963433</c:v>
+                  <c:v>99.647697005848002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99.78724727476758</c:v>
+                  <c:v>99.787223831636666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99.871888014082145</c:v>
+                  <c:v>99.871872486073485</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99.9230198954873</c:v>
+                  <c:v>99.923009638998025</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99.953838322933933</c:v>
+                  <c:v>99.953831574348371</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99.972407392485152</c:v>
+                  <c:v>99.972402982706726</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.983628614798249</c:v>
+                  <c:v>99.983625774391285</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99.990480443846337</c:v>
+                  <c:v>99.990478672321331</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.994788052963884</c:v>
+                  <c:v>99.994787032430708</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.997701553563218</c:v>
+                  <c:v>99.997701092869505</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>100</c:v>
@@ -4489,76 +4489,76 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.291887646433864</c:v>
+                  <c:v>22.291631406764335</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.393238588558596</c:v>
+                  <c:v>40.392763245500014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54.120471845272291</c:v>
+                  <c:v>54.119830754443655</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>64.490406269933644</c:v>
+                  <c:v>64.489662931127981</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>72.511944979137127</c:v>
+                  <c:v>72.51116619367194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>78.918107088841367</c:v>
+                  <c:v>78.917355939952301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>84.17994409956259</c:v>
+                  <c:v>84.179273265583745</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.563314661100094</c:v>
+                  <c:v>88.562760454922127</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.168920129855948</c:v>
+                  <c:v>92.168497677066483</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94.963510451070619</c:v>
+                  <c:v>94.963211192866666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>96.875007157092455</c:v>
+                  <c:v>96.874802961063182</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>98.096018620345006</c:v>
+                  <c:v>98.095881682396765</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>98.850143532654087</c:v>
+                  <c:v>98.850052409881499</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99.308468040212716</c:v>
+                  <c:v>99.308407616608804</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99.584918091569378</c:v>
+                  <c:v>99.584878093447202</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99.751084708455778</c:v>
+                  <c:v>99.751058259983211</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99.850808519796942</c:v>
+                  <c:v>99.850791049987109</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99.910624381590793</c:v>
+                  <c:v>99.910612861597116</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99.946509775111736</c:v>
+                  <c:v>99.946502202466533</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99.96806684305858</c:v>
+                  <c:v>99.968061897519974</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.981068344735363</c:v>
+                  <c:v>99.98106516019692</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99.988997197900602</c:v>
+                  <c:v>99.988995212061212</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.99397778148662</c:v>
+                  <c:v>99.993976637585234</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.997344650456128</c:v>
+                  <c:v>99.997344134093254</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>100</c:v>
@@ -4593,76 +4593,76 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.629993135682618</c:v>
+                  <c:v>17.629675196316992</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33.332226968570289</c:v>
+                  <c:v>33.331637684183264</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.505697793464918</c:v>
+                  <c:v>46.504904330556997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>57.355547156504322</c:v>
+                  <c:v>57.354629711307126</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>66.341839959904092</c:v>
+                  <c:v>66.34088331413021</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>73.911583053378664</c:v>
+                  <c:v>73.910667966737549</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>80.406361090063541</c:v>
+                  <c:v>80.405556104303912</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>86.033870256323581</c:v>
+                  <c:v>86.03322409536446</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.835515612761014</c:v>
+                  <c:v>90.835049632229854</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94.610565432726276</c:v>
+                  <c:v>94.610264947331927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>96.889584276134997</c:v>
+                  <c:v>96.889393010437345</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>98.19747978303468</c:v>
+                  <c:v>98.197357074668133</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>98.946443838531309</c:v>
+                  <c:v>98.946364335325725</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99.379446805223495</c:v>
+                  <c:v>99.379394908057208</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99.632383532291271</c:v>
+                  <c:v>99.632349491348762</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99.781362454864961</c:v>
+                  <c:v>99.781340064861837</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99.869635335921572</c:v>
+                  <c:v>99.869620592294567</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99.922158259969734</c:v>
+                  <c:v>99.922148554936769</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99.953508849514563</c:v>
+                  <c:v>99.953502476400672</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99.972281404488967</c:v>
+                  <c:v>99.972277244709716</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.983580434553886</c:v>
+                  <c:v>99.983577756815194</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99.990462047673731</c:v>
+                  <c:v>99.990460378141336</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.994781133374829</c:v>
+                  <c:v>99.994780171755792</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.997699239978914</c:v>
+                  <c:v>99.997698805918304</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>100</c:v>
@@ -4697,76 +4697,76 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.895797389204184</c:v>
+                  <c:v>14.895431694319274</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.799885112853719</c:v>
+                  <c:v>28.799207964357365</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.214429315716558</c:v>
+                  <c:v>41.213519172291853</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52.08411741291463</c:v>
+                  <c:v>52.083068269411022</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61.588157623120125</c:v>
+                  <c:v>61.587069384801943</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>69.979907662675572</c:v>
+                  <c:v>69.978876508561626</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>77.499949551156746</c:v>
+                  <c:v>77.499059089528174</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>84.330216643831164</c:v>
+                  <c:v>84.329530190000611</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.528659279102243</c:v>
+                  <c:v>90.528211809155664</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>95.753625427065643</c:v>
+                  <c:v>95.75340595379339</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>97.875269274073332</c:v>
+                  <c:v>97.875147058685826</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>98.857862757302243</c:v>
+                  <c:v>98.857789270512484</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>99.358699067598309</c:v>
+                  <c:v>99.358652948695934</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99.630487812126916</c:v>
+                  <c:v>99.630458188945482</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99.78380416649307</c:v>
+                  <c:v>99.78378489902876</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99.872344531321318</c:v>
+                  <c:v>99.87233191582078</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99.924210985895996</c:v>
+                  <c:v>99.924202699392509</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99.954863736527329</c:v>
+                  <c:v>99.954858289454734</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99.973085477743325</c:v>
+                  <c:v>99.9730819034896</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99.983969180074112</c:v>
+                  <c:v>99.983966848103037</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.990509745024127</c:v>
+                  <c:v>99.990508244212833</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99.99448930756553</c:v>
+                  <c:v>99.994488371933102</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.996985404256264</c:v>
+                  <c:v>99.996984865378266</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.998671161058795</c:v>
+                  <c:v>99.998670917824143</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>100</c:v>
@@ -4803,31 +4803,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.153242952970206</c:v>
+                  <c:v>13.152843616601507</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.756982056144217</c:v>
+                  <c:v>25.756243306633184</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.467887349118435</c:v>
+                  <c:v>37.466896124839693</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.17819407381181</c:v>
+                  <c:v>48.177054809240637</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>57.94662528301852</c:v>
+                  <c:v>57.945449447102376</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66.919813750168061</c:v>
+                  <c:v>66.918709593176558</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>75.283209774684991</c:v>
+                  <c:v>75.282273555244657</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>83.258315314765099</c:v>
+                  <c:v>83.257625765952852</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>91.19524140872889</c:v>
+                  <c:v>91.194861460598148</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -4909,31 +4909,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.960118701345277</c:v>
+                  <c:v>11.959699465452246</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23.606800437440675</c:v>
+                  <c:v>23.606025520732157</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.721805399418905</c:v>
+                  <c:v>34.720767211190605</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45.213995691496031</c:v>
+                  <c:v>45.212805395606757</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55.100187574256672</c:v>
+                  <c:v>55.098964001187724</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>64.469380102550176</c:v>
+                  <c:v>64.468238861795214</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>73.454655793258326</c:v>
+                  <c:v>73.453699772319197</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82.224525516119684</c:v>
+                  <c:v>82.223837857966771</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.993968132506922</c:v>
+                  <c:v>90.993608267283633</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -4970,31 +4970,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.080354862447127</c:v>
+                  <c:v>11.079928724473955</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.988179233298098</c:v>
+                  <c:v>21.987392099650521</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32.598395089755371</c:v>
+                  <c:v>32.597341803581259</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42.855640874620335</c:v>
+                  <c:v>42.854435560805292</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.770597709878501</c:v>
+                  <c:v>52.769362300243841</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62.402729222469603</c:v>
+                  <c:v>62.401582080494954</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>71.841403113559423</c:v>
+                  <c:v>71.840448814268257</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81.191096600516147</c:v>
+                  <c:v>81.190417626310222</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.556083306964297</c:v>
+                  <c:v>90.555733750569217</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5031,31 +5031,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.37304435826502</c:v>
+                  <c:v>10.372623332791683</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.667049623378141</c:v>
+                  <c:v>20.66627234981263</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.827811490478741</c:v>
+                  <c:v>30.826772342676083</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>40.83942024884044</c:v>
+                  <c:v>40.83823274378657</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.723682311176461</c:v>
+                  <c:v>50.722467558484723</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60.529403171778888</c:v>
+                  <c:v>60.528278345670145</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.31702793725438</c:v>
+                  <c:v>70.316095777946799</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>80.142309987720992</c:v>
+                  <c:v>80.14165008243549</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.039246904981283</c:v>
+                  <c:v>90.038909108682631</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5092,31 +5092,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.7446972941567065</c:v>
+                  <c:v>9.7442922568788113</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.479049080168743</c:v>
+                  <c:v>19.478301624130207</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>29.206241100132431</c:v>
+                  <c:v>29.205242473521409</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38.950395624942544</c:v>
+                  <c:v>38.949255513177505</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>48.755161602912708</c:v>
+                  <c:v>48.753996844235743</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>58.674044672708334</c:v>
+                  <c:v>58.672967965751845</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>68.754896275579597</c:v>
+                  <c:v>68.754005869411586</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>79.021806651519356</c:v>
+                  <c:v>79.021177816801213</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>89.458573761479386</c:v>
+                  <c:v>89.458252601725434</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5153,31 +5153,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.1266234970322895</c:v>
+                  <c:v>9.1262440705920831</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.298099403036066</c:v>
+                  <c:v>18.297399416306064</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27.56757518426452</c:v>
+                  <c:v>27.566640414099489</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.00061650728172</c:v>
+                  <c:v>36.999549991163775</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.672384995150637</c:v>
+                  <c:v>46.671296339526478</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56.656596123558188</c:v>
+                  <c:v>56.655590803687772</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>67.006612306178326</c:v>
+                  <c:v>67.005781917144844</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77.731388447444246</c:v>
+                  <c:v>77.73080271363132</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.773222322773748</c:v>
+                  <c:v>88.772923481417564</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5215,31 +5215,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.4636301484337331</c:v>
+                  <c:v>8.4632846091822813</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.019048889384432</c:v>
+                  <c:v>17.018411556400721</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.765220599588179</c:v>
+                  <c:v>25.764369775404546</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.811978011722196</c:v>
+                  <c:v>34.811007697849291</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44.277037635870172</c:v>
+                  <c:v>44.276047719016375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54.27323055174714</c:v>
+                  <c:v>54.272316992325955</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>64.883482360766322</c:v>
+                  <c:v>64.882728281847164</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>76.123859195695104</c:v>
+                  <c:v>76.123327639160721</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>87.902909671166185</c:v>
+                  <c:v>87.902638610313147</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5277,31 +5277,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.708787609292842</c:v>
+                  <c:v>7.708482809735262</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.549154528007088</c:v>
+                  <c:v>15.548592424708399</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.662169657415212</c:v>
+                  <c:v>23.661419433266754</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32.204918638849918</c:v>
+                  <c:v>32.204063305810408</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>41.350442149826172</c:v>
+                  <c:v>41.349569846361774</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51.275705863005861</c:v>
+                  <c:v>51.274901164750744</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>62.130150528094127</c:v>
+                  <c:v>62.129486578755817</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.977608798023482</c:v>
+                  <c:v>73.977140950850412</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.714541826196964</c:v>
+                  <c:v>86.714303320674048</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5339,31 +5339,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.8223128947817999</c:v>
+                  <c:v>6.822054205049449</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.806532915348253</c:v>
+                  <c:v>13.806055899429488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21.129288787386873</c:v>
+                  <c:v>21.128652227141995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.994981845752374</c:v>
+                  <c:v>28.994256245762013</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>37.64400702005068</c:v>
+                  <c:v>37.643267195867836</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>47.348913555253702</c:v>
+                  <c:v>47.348231241557926</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>58.383738746036855</c:v>
+                  <c:v>58.383175917573801</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>70.941842768290115</c:v>
+                  <c:v>70.941446264810324</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>84.977635822663444</c:v>
+                  <c:v>84.977433721532421</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5401,31 +5401,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7738868364929612</c:v>
+                  <c:v>5.7736781110322788</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.725309594094737</c:v>
+                  <c:v>11.724924740816963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.05339084735639</c:v>
+                  <c:v>18.052877330108345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25.001627522289425</c:v>
+                  <c:v>25.001042254226348</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32.881608099910643</c:v>
+                  <c:v>32.881011449788197</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>42.09213086794923</c:v>
+                  <c:v>42.091580688038064</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>53.113993346597503</c:v>
+                  <c:v>53.113539585170173</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>66.428354092143252</c:v>
+                  <c:v>66.4280344692841</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>82.254148198229359</c:v>
+                  <c:v>82.253985300645127</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5463,31 +5463,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5478899231660002</c:v>
+                  <c:v>4.5477334982621</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.2673760275937269</c:v>
+                  <c:v>9.2670876226968435</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.357274894944094</c:v>
+                  <c:v>14.356890098246987</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.076462515040781</c:v>
+                  <c:v>20.076023991245663</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26.788602669001534</c:v>
+                  <c:v>26.788155661019434</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.023952625759563</c:v>
+                  <c:v>35.023540475635002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>45.551707153106925</c:v>
+                  <c:v>45.551367265783988</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>59.403406117352624</c:v>
+                  <c:v>59.403166726510335</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>77.610595010782504</c:v>
+                  <c:v>77.610473011763858</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5525,31 +5525,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1502715337069551</c:v>
+                  <c:v>3.1501682593188409</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.4389925570143305</c:v>
+                  <c:v>6.4388021534606796</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.031825478656911</c:v>
+                  <c:v>10.031571448936331</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.158297434509802</c:v>
+                  <c:v>14.158007951489068</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.17234179343502</c:v>
+                  <c:v>19.172046727408073</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25.663330327451991</c:v>
+                  <c:v>25.663058287697851</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>34.665446605151089</c:v>
+                  <c:v>34.665222275819936</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>48.022950151642782</c:v>
+                  <c:v>48.022792159209089</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>68.784820533360545</c:v>
+                  <c:v>68.784740019899857</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -5586,31 +5586,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6141880787586909</c:v>
+                  <c:v>1.6141373855523151</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.3064747427656602</c:v>
+                  <c:v>3.3063812828903156</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.1727102806627858</c:v>
+                  <c:v>5.1725855925481286</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.3525317245539661</c:v>
+                  <c:v>7.3523896383657092</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.079109831512593</c:v>
+                  <c:v>10.078965009425481</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13.791557188240112</c:v>
+                  <c:v>13.791423671927991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.423781487477637</c:v>
+                  <c:v>19.42367139058851</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.238117152534315</c:v>
+                  <c:v>29.238039614606031</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>49.505734421473718</c:v>
+                  <c:v>49.505694908626474</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>100</c:v>
@@ -6458,22 +6458,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6482,19 +6482,19 @@
       </c>
       <c r="F8">
         <f ca="1">AVERAGE(F7,E8,G8,F9)</f>
-        <v>2.9205185855377112</v>
+        <v>46.760874156915555</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:I15" ca="1" si="0">AVERAGE(G7,F8,H8,G9)</f>
-        <v>3.2080015526114058</v>
+        <v>60.628756018183708</v>
       </c>
       <c r="H8">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2081136783391813</v>
+        <v>60.628756018183708</v>
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="0"/>
-        <v>2.9207276203504913</v>
+        <v>46.760874156915555</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -6505,20 +6505,20 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <f t="shared" ref="F9:F15" ca="1" si="1">AVERAGE(F8,E9,G9,F10)</f>
-        <v>2.4746655980759469</v>
+        <f ca="1">AVERAGE(F8,E9,G9,F10)</f>
+        <v>24.41474060947851</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7040679671568366</v>
+        <v>35.125393897635561</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7042541907158975</v>
+        <v>35.125393897635561</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="0"/>
-        <v>2.4750128212445475</v>
+        <v>24.41474060947851</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -6529,20 +6529,20 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.2749128302251114</v>
+        <f t="shared" ref="F9:F15" ca="1" si="1">AVERAGE(F9,E10,G10,F11)</f>
+        <v>13.772694383362921</v>
       </c>
       <c r="G10">
         <f t="shared" ca="1" si="0"/>
-        <v>2.4302917706715625</v>
+        <v>20.332685065244473</v>
       </c>
       <c r="H10">
         <f t="shared" ca="1" si="0"/>
-        <v>2.430513800461676</v>
+        <v>20.332685065244473</v>
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="0"/>
-        <v>2.2753268812701228</v>
+        <v>13.772694383362921</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -6554,19 +6554,19 @@
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="1"/>
-        <v>2.1956231189460365</v>
+        <v>8.3433518587287026</v>
       </c>
       <c r="G11">
         <f t="shared" ca="1" si="0"/>
-        <v>2.312695068226883</v>
+        <v>12.09996691473494</v>
       </c>
       <c r="H11">
         <f t="shared" ca="1" si="0"/>
-        <v>2.3129184240870355</v>
+        <v>12.09996691473494</v>
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="0"/>
-        <v>2.1960397066405215</v>
+        <v>8.3433518587287026</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -6578,19 +6578,19 @@
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="1"/>
-        <v>2.1957740165689472</v>
+        <v>5.500746136816951</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="0"/>
-        <v>2.3129096482248661</v>
+        <v>7.6238638202316471</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="0"/>
-        <v>2.3131069089776251</v>
+        <v>7.6238638202316462</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="0"/>
-        <v>2.196141981610638</v>
+        <v>5.500746136816951</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -6602,19 +6602,19 @@
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2753131477531729</v>
+        <v>4.0357688683074544</v>
       </c>
       <c r="G13">
         <f t="shared" ca="1" si="0"/>
-        <v>2.4308610543029929</v>
+        <v>5.2708784091430489</v>
       </c>
       <c r="H13">
         <f t="shared" ca="1" si="0"/>
-        <v>2.4310138716821026</v>
+        <v>5.2708784091430489</v>
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="0"/>
-        <v>2.2755982371208536</v>
+        <v>4.0357688683074544</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -6626,19 +6626,19 @@
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="1"/>
-        <v>2.4751665396003455</v>
+        <v>3.3714509272698181</v>
       </c>
       <c r="G14">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7047803741447316</v>
+        <v>4.1530025388900462</v>
       </c>
       <c r="H14">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7048800077537827</v>
+        <v>4.1530025388900462</v>
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="0"/>
-        <v>2.4753524227929278</v>
+        <v>3.3714509272698181</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -6650,19 +6650,19 @@
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="1"/>
-        <v>2.9208985574131363</v>
+        <v>3.2970323018817727</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2085419053888726</v>
+        <v>3.816678280257273</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2085883398599324</v>
+        <v>3.816678280257273</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="0"/>
-        <v>2.9209851906632149</v>
+        <v>3.2970323018817727</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -6766,75 +6766,75 @@
       </c>
       <c r="B2">
         <f ca="1">AVERAGE(B1,A2,C2,B3)</f>
-        <v>99.504991077436145</v>
+        <v>99.506101147438727</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:S16" ca="1" si="0">AVERAGE(C1,B2,D2,C3)</f>
-        <v>99.005724669931354</v>
+        <f t="shared" ref="C2:S2" ca="1" si="0">AVERAGE(C1,B2,D2,C3)</f>
+        <v>99.007892337956008</v>
       </c>
       <c r="D2">
         <f t="shared" ca="1" si="0"/>
-        <v>98.49753769133622</v>
+        <v>98.500683437493734</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>97.974918765651353</v>
+        <v>97.978938554240187</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>97.430983277458779</v>
+        <v>97.435751678373947</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>96.856798601422923</v>
+        <v>96.862172428043706</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>96.240451431901022</v>
+        <v>96.246273808444414</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>95.565673570560463</v>
+        <v>95.571778328083099</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>94.809698976866784</v>
+        <v>94.81591526459512</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>93.939739718919341</v>
+        <v>93.945896707410441</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>92.906869465311161</v>
+        <v>92.912801011094786</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>91.634760921390296</v>
+        <v>91.640310060086222</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>89.997487613557524</v>
+        <v>90.002510750638208</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>87.772140728371028</v>
+        <v>87.776511404075464</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>84.527895571282613</v>
+        <v>84.531507688661193</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>79.338065080963617</v>
+        <v>79.340835503258162</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>69.947002526199483</v>
+        <v>69.948872971016058</v>
       </c>
       <c r="S2">
-        <f t="shared" ca="1" si="0"/>
-        <v>50.089985405518846</v>
+        <f ca="1">AVERAGE(S1,R2,T2,S3)</f>
+        <v>50.09092358752828</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6846,75 +6846,75 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B25" ca="1" si="1">AVERAGE(B2,A3,C3,B4)</f>
-        <v>99.01423871722298</v>
+        <v>99.016419031854099</v>
       </c>
       <c r="C3">
-        <f t="shared" ca="1" si="0"/>
-        <v>98.020368341172968</v>
+        <f t="shared" ref="C2:S16" ca="1" si="2">AVERAGE(C2,B3,D3,C4)</f>
+        <v>98.024625843850046</v>
       </c>
       <c r="D3">
-        <f t="shared" ca="1" si="0"/>
-        <v>97.009505169187932</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>97.015683591986601</v>
       </c>
       <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>95.971151413640612</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>95.979046331498083</v>
       </c>
       <c r="F3">
-        <f t="shared" ca="1" si="0"/>
-        <v>94.892212626750648</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>94.901577599876745</v>
       </c>
       <c r="G3">
-        <f t="shared" ca="1" si="0"/>
-        <v>93.755756238254804</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>93.766309968386736</v>
       </c>
       <c r="H3">
-        <f t="shared" ca="1" si="0"/>
-        <v>92.53932985651231</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>92.550764184908985</v>
       </c>
       <c r="I3">
-        <f t="shared" ca="1" si="0"/>
-        <v>91.212540038738979</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>91.224528586930859</v>
       </c>
       <c r="J3">
-        <f t="shared" ca="1" si="0"/>
-        <v>89.733378754449063</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>89.745585984530251</v>
       </c>
       <c r="K3">
-        <f t="shared" ca="1" si="0"/>
-        <v>88.042386646475208</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88.054477098111448</v>
       </c>
       <c r="L3">
-        <f t="shared" ca="1" si="0"/>
-        <v>86.05297361141389</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>86.064621059671381</v>
       </c>
       <c r="M3">
-        <f t="shared" ca="1" si="0"/>
-        <v>83.634683268691177</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>83.645579541928782</v>
       </c>
       <c r="N3">
-        <f t="shared" ca="1" si="0"/>
-        <v>80.583045822633224</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>80.592909024263349</v>
       </c>
       <c r="O3">
-        <f t="shared" ca="1" si="0"/>
-        <v>76.563177176155946</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>76.571759068683974</v>
       </c>
       <c r="P3">
-        <f t="shared" ca="1" si="0"/>
-        <v>71.001374412635457</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>71.008466746973056</v>
       </c>
       <c r="Q3">
-        <f t="shared" ca="1" si="0"/>
-        <v>62.877360697974972</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>62.882800304829047</v>
       </c>
       <c r="R3">
-        <f t="shared" ca="1" si="0"/>
-        <v>50.359958654651777</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>50.363631156406115</v>
       </c>
       <c r="S3">
-        <f t="shared" ca="1" si="0"/>
-        <v>30.412938710970952</v>
+        <f t="shared" ref="S3:S25" ca="1" si="3">AVERAGE(S2,R3,T3,S4)</f>
+        <v>30.414780759950428</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6926,75 +6926,75 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="1"/>
-        <v>98.53159387000089</v>
+        <v>98.534789196420718</v>
       </c>
       <c r="C4">
-        <f t="shared" ca="1" si="0"/>
-        <v>97.052002177174188</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>97.058241586206222</v>
       </c>
       <c r="D4">
-        <f t="shared" ca="1" si="0"/>
-        <v>95.548959642334609</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>95.558013988676421</v>
       </c>
       <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>94.00796466534365</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>94.019534222886492</v>
       </c>
       <c r="F4">
-        <f t="shared" ca="1" si="0"/>
-        <v>92.410954448614461</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>92.424677929450311</v>
       </c>
       <c r="G4">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.734678191905061</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.750143250183214</v>
       </c>
       <c r="H4">
-        <f t="shared" ca="1" si="0"/>
-        <v>88.948565658879829</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88.965320625558547</v>
       </c>
       <c r="I4">
-        <f t="shared" ca="1" si="0"/>
-        <v>87.011771705664884</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>87.029338261151608</v>
       </c>
       <c r="J4">
-        <f t="shared" ca="1" si="0"/>
-        <v>84.868883052790864</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>84.886769509427026</v>
       </c>
       <c r="K4">
-        <f t="shared" ca="1" si="0"/>
-        <v>82.443448334598443</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>82.461163172749053</v>
       </c>
       <c r="L4">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.627949199252669</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.645014482168108</v>
       </c>
       <c r="M4">
-        <f t="shared" ca="1" si="0"/>
-        <v>76.267947306526167</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>76.283911592533926</v>
       </c>
       <c r="N4">
-        <f t="shared" ca="1" si="0"/>
-        <v>72.136830409435746</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>72.151280787125003</v>
       </c>
       <c r="O4">
-        <f t="shared" ca="1" si="0"/>
-        <v>66.896143626460429</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>66.908716520209722</v>
       </c>
       <c r="P4">
-        <f t="shared" ca="1" si="0"/>
-        <v>60.037060895115033</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>60.047451324471581</v>
       </c>
       <c r="Q4">
-        <f t="shared" ca="1" si="0"/>
-        <v>50.810042210623308</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>50.818011236552849</v>
       </c>
       <c r="R4">
-        <f t="shared" ca="1" si="0"/>
-        <v>38.202531174582973</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>38.20791132641547</v>
       </c>
       <c r="S4">
-        <f t="shared" ca="1" si="0"/>
-        <v>21.201810220087264</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>21.204508766253443</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7006,75 +7006,75 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="1"/>
-        <v>98.060132386549498</v>
+        <v>98.064273154364471</v>
       </c>
       <c r="C5">
-        <f t="shared" ca="1" si="0"/>
-        <v>96.107083226693248</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>96.115168612613303</v>
       </c>
       <c r="D5">
-        <f t="shared" ca="1" si="0"/>
-        <v>94.126361628632054</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>94.138094507281949</v>
       </c>
       <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>92.100787088694375</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>92.115778867045918</v>
       </c>
       <c r="F5">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.00895529210699</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.026737619329452</v>
       </c>
       <c r="G5">
-        <f t="shared" ca="1" si="0"/>
-        <v>87.823428663796989</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>87.843467063896185</v>
       </c>
       <c r="H5">
-        <f t="shared" ca="1" si="0"/>
-        <v>85.50847460971741</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>85.530183705663788</v>
       </c>
       <c r="I5">
-        <f t="shared" ca="1" si="0"/>
-        <v>83.017089522041701</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>83.039849469919176</v>
       </c>
       <c r="J5">
-        <f t="shared" ca="1" si="0"/>
-        <v>80.286924825423938</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>80.310098532330102</v>
       </c>
       <c r="K5">
-        <f t="shared" ca="1" si="0"/>
-        <v>77.234566041716704</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>77.257516705306855</v>
       </c>
       <c r="L5">
-        <f t="shared" ca="1" si="0"/>
-        <v>73.747419562640914</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>73.769528046830573</v>
       </c>
       <c r="M5">
-        <f t="shared" ca="1" si="0"/>
-        <v>69.672318990612936</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>69.693000544048132</v>
       </c>
       <c r="N5">
-        <f t="shared" ca="1" si="0"/>
-        <v>64.800178333779726</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>64.818898167427719</v>
       </c>
       <c r="O5">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.847500446682467</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>58.863787715365135</v>
       </c>
       <c r="P5">
-        <f t="shared" ca="1" si="0"/>
-        <v>51.440678852589926</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>51.454138632304243</v>
       </c>
       <c r="Q5">
-        <f t="shared" ca="1" si="0"/>
-        <v>42.123212794771625</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>42.133535711761013</v>
       </c>
       <c r="R5">
-        <f t="shared" ca="1" si="0"/>
-        <v>30.438311594262338</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>30.445280840371026</v>
       </c>
       <c r="S5">
-        <f t="shared" ca="1" si="0"/>
-        <v>16.191770265132639</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>16.195265823356426</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7086,75 +7086,75 @@
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="1"/>
-        <v>97.601849679480623</v>
+        <v>97.6068532308702</v>
       </c>
       <c r="C6">
-        <f t="shared" ca="1" si="0"/>
-        <v>95.189832166981162</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>95.199602045249961</v>
       </c>
       <c r="D6">
-        <f t="shared" ca="1" si="0"/>
-        <v>92.748610393242217</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>92.762787332118279</v>
       </c>
       <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.259859190632056</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.277973397208399</v>
       </c>
       <c r="F6">
-        <f t="shared" ca="1" si="0"/>
-        <v>87.700642210405007</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>87.722127541916421</v>
       </c>
       <c r="G6">
-        <f t="shared" ca="1" si="0"/>
-        <v>85.04159688823367</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>85.065807350412683</v>
       </c>
       <c r="H6">
-        <f t="shared" ca="1" si="0"/>
-        <v>82.244804286375967</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>82.271032450438668</v>
       </c>
       <c r="I6">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.261176297956894</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.288673173170764</v>
       </c>
       <c r="J6">
-        <f t="shared" ca="1" si="0"/>
-        <v>76.027149990023048</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>76.055145835394939</v>
       </c>
       <c r="K6">
-        <f t="shared" ca="1" si="0"/>
-        <v>72.460460994173246</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>72.488186510323047</v>
       </c>
       <c r="L6">
-        <f t="shared" ca="1" si="0"/>
-        <v>68.454834091989497</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>68.481541406880993</v>
       </c>
       <c r="M6">
-        <f t="shared" ca="1" si="0"/>
-        <v>63.87372161337224</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>63.898704466806699</v>
       </c>
       <c r="N6">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.544055354254454</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>58.566667898446006</v>
       </c>
       <c r="O6">
-        <f t="shared" ca="1" si="0"/>
-        <v>52.252994050533125</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>52.272667718923998</v>
       </c>
       <c r="P6">
-        <f t="shared" ca="1" si="0"/>
-        <v>44.754935722891062</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>44.771193676384407</v>
       </c>
       <c r="Q6">
-        <f t="shared" ca="1" si="0"/>
-        <v>35.80381446422404</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>35.816283201447135</v>
       </c>
       <c r="R6">
-        <f t="shared" ca="1" si="0"/>
-        <v>25.235729656668301</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>25.244147469548295</v>
       </c>
       <c r="S6">
-        <f t="shared" ca="1" si="0"/>
-        <v>13.126958365504287</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>13.131180428988982</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7166,75 +7166,75 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>97.157430879161083</v>
+        <v>97.163202885582564</v>
       </c>
       <c r="C7">
         <f ca="1">AVERAGE(C6,B7,D7,C8)</f>
-        <v>94.30177999327482</v>
+        <v>94.3130500957935</v>
       </c>
       <c r="D7">
-        <f t="shared" ca="1" si="0"/>
-        <v>91.418381311896837</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>91.434734787701288</v>
       </c>
       <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>88.489388133579013</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88.510282761263582</v>
       </c>
       <c r="F7">
-        <f t="shared" ca="1" si="0"/>
-        <v>85.492147150013523</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>85.516929594884829</v>
       </c>
       <c r="G7">
-        <f t="shared" ca="1" si="0"/>
-        <v>82.397500997011747</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>82.425425872238861</v>
       </c>
       <c r="H7">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.167957211357276</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.198208347160545</v>
       </c>
       <c r="I7">
-        <f t="shared" ca="1" si="0"/>
-        <v>75.755648857100624</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>75.787362241443304</v>
       </c>
       <c r="J7">
-        <f t="shared" ca="1" si="0"/>
-        <v>72.100025256454799</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>72.132313049905861</v>
       </c>
       <c r="K7">
-        <f t="shared" ca="1" si="0"/>
-        <v>68.125281559227901</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>68.15725653861719</v>
       </c>
       <c r="L7">
-        <f t="shared" ca="1" si="0"/>
-        <v>63.737722523280574</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>63.768522278138178</v>
       </c>
       <c r="M7">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.823667264503705</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>58.852477461057688</v>
       </c>
       <c r="N7">
-        <f t="shared" ca="1" si="0"/>
-        <v>53.249317861199863</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>53.275393903756481</v>
       </c>
       <c r="O7">
-        <f t="shared" ca="1" si="0"/>
-        <v>46.865476547628042</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46.888163007846792</v>
       </c>
       <c r="P7">
-        <f t="shared" ca="1" si="0"/>
-        <v>39.522249010776335</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>39.540996261359389</v>
       </c>
       <c r="Q7">
-        <f t="shared" ca="1" si="0"/>
-        <v>31.101374928249992</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>31.115752506846224</v>
       </c>
       <c r="R7">
-        <f t="shared" ca="1" si="0"/>
-        <v>21.573831298673653</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>21.58353763670338</v>
       </c>
       <c r="S7">
-        <f t="shared" ca="1" si="0"/>
-        <v>11.080332525599584</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>11.085200800260612</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -7246,75 +7246,75 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>96.72609010611319</v>
+        <v>96.732526136025641</v>
       </c>
       <c r="C8">
-        <f t="shared" ca="1" si="0"/>
-        <v>93.44146951423113</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>93.454035855580713</v>
       </c>
       <c r="D8">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.133738479527821</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.151972374740581</v>
       </c>
       <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>86.787154756158841</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>86.810451288030009</v>
       </c>
       <c r="F8">
-        <f t="shared" ca="1" si="0"/>
-        <v>83.381045570390057</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>83.408675967197382</v>
       </c>
       <c r="G8">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.888289836941709</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.919422758538431</v>
       </c>
       <c r="H8">
-        <f t="shared" ca="1" si="0"/>
-        <v>76.273860966198143</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>76.307586246207705</v>
       </c>
       <c r="I8">
-        <f t="shared" ca="1" si="0"/>
-        <v>72.493422476888099</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>72.528776720145856</v>
       </c>
       <c r="J8">
-        <f t="shared" ca="1" si="0"/>
-        <v>68.49200638071764</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>68.527999748218051</v>
       </c>
       <c r="K8">
-        <f t="shared" ca="1" si="0"/>
-        <v>64.202903558248423</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>64.238547019324528</v>
       </c>
       <c r="L8">
-        <f t="shared" ca="1" si="0"/>
-        <v>59.547093976305867</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>59.581426274683011</v>
       </c>
       <c r="M8">
-        <f t="shared" ca="1" si="0"/>
-        <v>54.433894905407158</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>54.46600847647796</v>
       </c>
       <c r="N8">
-        <f t="shared" ca="1" si="0"/>
-        <v>48.764061476988005</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>48.793126571239384</v>
       </c>
       <c r="O8">
-        <f t="shared" ca="1" si="0"/>
-        <v>42.437336083649917</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>42.462622397092474</v>
       </c>
       <c r="P8">
-        <f t="shared" ca="1" si="0"/>
-        <v>35.367201491329972</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>35.388096677635801</v>
       </c>
       <c r="Q8">
-        <f t="shared" ca="1" si="0"/>
-        <v>27.5055995777244</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>27.521624116283196</v>
       </c>
       <c r="R8">
-        <f t="shared" ca="1" si="0"/>
-        <v>18.877884816645189</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>18.888702831853067</v>
       </c>
       <c r="S8">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.6205393084776389</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>9.6259650727813035</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -7326,75 +7326,75 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>96.305455909173332</v>
+        <v>96.312443128957028</v>
       </c>
       <c r="C9">
-        <f t="shared" ca="1" si="0"/>
-        <v>92.604262763002623</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>92.617904966307037</v>
       </c>
       <c r="D9">
-        <f t="shared" ca="1" si="0"/>
-        <v>88.887939265187697</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88.907733701053033</v>
       </c>
       <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>85.144435711111967</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>85.169725304540265</v>
       </c>
       <c r="F9">
-        <f t="shared" ca="1" si="0"/>
-        <v>81.356577694737453</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>81.386570957148663</v>
       </c>
       <c r="G9">
-        <f t="shared" ca="1" si="0"/>
-        <v>77.500737641522818</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>77.53453181442643</v>
       </c>
       <c r="H9">
-        <f t="shared" ca="1" si="0"/>
-        <v>73.545759250549935</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>73.582366109130774</v>
       </c>
       <c r="I9">
-        <f t="shared" ca="1" si="0"/>
-        <v>69.452158126595833</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>69.490531788137673</v>
       </c>
       <c r="J9">
-        <f t="shared" ca="1" si="0"/>
-        <v>65.171658599028888</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>65.210724609451972</v>
       </c>
       <c r="K9">
-        <f t="shared" ca="1" si="0"/>
-        <v>60.647217053994417</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>60.685901969867629</v>
       </c>
       <c r="L9">
-        <f t="shared" ca="1" si="0"/>
-        <v>55.813840430746716</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>55.851101079358976</v>
       </c>
       <c r="M9">
-        <f t="shared" ca="1" si="0"/>
-        <v>50.600743567509355</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>50.635595158545328</v>
       </c>
       <c r="N9">
-        <f t="shared" ca="1" si="0"/>
-        <v>44.935685209356464</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>44.967227491670251</v>
       </c>
       <c r="O9">
-        <f t="shared" ca="1" si="0"/>
-        <v>38.752594747529095</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>38.780035454950628</v>
       </c>
       <c r="P9">
-        <f t="shared" ca="1" si="0"/>
-        <v>32.003613234135784</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>32.026288144701468</v>
       </c>
       <c r="Q9">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.67593120305196</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>24.693320244026836</v>
       </c>
       <c r="R9">
-        <f t="shared" ca="1" si="0"/>
-        <v>16.811565509787947</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>16.823304471973962</v>
       </c>
       <c r="S9">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5239386670173261</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>8.5298262402044784</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7406,75 +7406,75 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>95.891466334584251</v>
+        <v>95.898885322296195</v>
       </c>
       <c r="C10">
-        <f t="shared" ca="1" si="0"/>
-        <v>91.782179152921202</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>91.796663995306076</v>
       </c>
       <c r="D10">
-        <f t="shared" ca="1" si="0"/>
-        <v>87.669310373970518</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>87.690326860999221</v>
       </c>
       <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>83.546059190355095</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>83.572909265255689</v>
       </c>
       <c r="F10">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.400078083763418</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.431921023580784</v>
       </c>
       <c r="G10">
-        <f t="shared" ca="1" si="0"/>
-        <v>75.212308590034553</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>75.248185615848996</v>
       </c>
       <c r="H10">
-        <f t="shared" ca="1" si="0"/>
-        <v>70.956264094571935</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>70.995125799027861</v>
       </c>
       <c r="I10">
         <f ca="1">AVERAGE(I9,H10,J10,I11)</f>
-        <v>66.597775486382176</v>
+        <v>66.638511380092751</v>
       </c>
       <c r="J10">
-        <f t="shared" ca="1" si="0"/>
-        <v>62.095236084576158</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>62.136705487907527</v>
       </c>
       <c r="K10">
-        <f t="shared" ca="1" si="0"/>
-        <v>57.400449276164196</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>57.44151272469778</v>
       </c>
       <c r="L10">
-        <f t="shared" ca="1" si="0"/>
-        <v>52.460291606427745</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>52.499841902667981</v>
       </c>
       <c r="M10">
-        <f t="shared" ca="1" si="0"/>
-        <v>47.219539441536448</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>47.256531476931499</v>
       </c>
       <c r="N10">
-        <f t="shared" ca="1" si="0"/>
-        <v>41.625328358776436</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>41.658806852198929</v>
       </c>
       <c r="O10">
-        <f t="shared" ca="1" si="0"/>
-        <v>35.633733682346701</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>35.66285803535586</v>
       </c>
       <c r="P10">
-        <f t="shared" ca="1" si="0"/>
-        <v>29.218716871347439</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>29.242782426272132</v>
       </c>
       <c r="Q10">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.382940212121206</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>22.40139531360213</v>
       </c>
       <c r="R10">
-        <f t="shared" ca="1" si="0"/>
-        <v>15.168503538789611</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>15.180961938286632</v>
       </c>
       <c r="S10">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.6636485515287198</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7.6698968512084473</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -7486,75 +7486,75 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>95.478225608475356</v>
+        <v>95.485952257386487</v>
       </c>
       <c r="C11">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.963669558071814</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.978754690470709</v>
       </c>
       <c r="D11">
-        <f t="shared" ca="1" si="0"/>
-        <v>86.461053658934659</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>86.482940498931256</v>
       </c>
       <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>81.970400051506743</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>81.998361198012901</v>
       </c>
       <c r="F11">
-        <f t="shared" ca="1" si="0"/>
-        <v>77.485352395641343</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>77.518511922310807</v>
       </c>
       <c r="G11">
-        <f t="shared" ca="1" si="0"/>
-        <v>72.992138585926995</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>73.029497709424305</v>
       </c>
       <c r="H11">
-        <f t="shared" ca="1" si="0"/>
-        <v>68.46919607115727</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>68.509661746310485</v>
       </c>
       <c r="I11">
-        <f t="shared" ca="1" si="0"/>
-        <v>63.887426115927482</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>63.929841827428326</v>
       </c>
       <c r="J11">
         <f ca="1">AVERAGE(J10,I11,K11,J12)</f>
-        <v>59.211043395708664</v>
+        <v>59.254221338886758</v>
       </c>
       <c r="K11">
-        <f t="shared" ca="1" si="0"/>
-        <v>54.399035199137622</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>54.441788982911305</v>
       </c>
       <c r="L11">
-        <f t="shared" ca="1" si="0"/>
-        <v>49.407320993284749</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>49.448497962399955</v>
       </c>
       <c r="M11">
-        <f t="shared" ca="1" si="0"/>
-        <v>44.191779248520319</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>44.23029151446228</v>
       </c>
       <c r="N11">
-        <f t="shared" ca="1" si="0"/>
-        <v>38.712341794296492</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>38.747195088173129</v>
       </c>
       <c r="O11">
-        <f t="shared" ca="1" si="0"/>
-        <v>32.938283446228198</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>32.968602963977645</v>
       </c>
       <c r="P11">
-        <f t="shared" ca="1" si="0"/>
-        <v>26.854571316859197</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>26.879623816703393</v>
       </c>
       <c r="Q11">
-        <f t="shared" ca="1" si="0"/>
-        <v>20.468602657424722</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>20.487814188793379</v>
       </c>
       <c r="R11">
-        <f t="shared" ca="1" si="0"/>
-        <v>13.815855891455188</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>13.828824678861533</v>
       </c>
       <c r="S11">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.9621506503871826</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6.9686548185187807</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -7562,80 +7562,80 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" ref="A12:A25" si="2">A11</f>
+        <f t="shared" ref="A12:A25" si="4">A11</f>
         <v>100</v>
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>95.057761717092234</v>
+        <v>95.065669203237746</v>
       </c>
       <c r="C12">
-        <f t="shared" ca="1" si="0"/>
-        <v>90.133211985461116</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>90.148649776277935</v>
       </c>
       <c r="D12">
-        <f t="shared" ca="1" si="0"/>
-        <v>85.240824099722758</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>85.26322196582133</v>
       </c>
       <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>80.389122026983557</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>80.417735138296536</v>
       </c>
       <c r="F12">
-        <f t="shared" ca="1" si="0"/>
-        <v>75.578777947106886</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>75.61270953154974</v>
       </c>
       <c r="G12">
-        <f t="shared" ca="1" si="0"/>
-        <v>70.801680839027227</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>70.839908489333965</v>
       </c>
       <c r="H12">
-        <f t="shared" ca="1" si="0"/>
-        <v>66.040937985331098</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>66.082342953889338</v>
       </c>
       <c r="I12">
-        <f t="shared" ca="1" si="0"/>
-        <v>61.271671449474219</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>61.315070180782584</v>
       </c>
       <c r="J12">
-        <f t="shared" ca="1" si="0"/>
-        <v>56.462458065484462</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>56.506635137957943</v>
       </c>
       <c r="K12">
-        <f t="shared" ca="1" si="0"/>
-        <v>51.577309449160602</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>51.621051038395841</v>
       </c>
       <c r="L12">
-        <f t="shared" ca="1" si="0"/>
-        <v>46.578161142157292</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46.620288082165771</v>
       </c>
       <c r="M12">
-        <f t="shared" ca="1" si="0"/>
-        <v>41.427899328670328</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>41.467298840810415</v>
       </c>
       <c r="N12">
-        <f t="shared" ca="1" si="0"/>
-        <v>36.093962417588905</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>36.129617602326057</v>
       </c>
       <c r="O12">
-        <f t="shared" ca="1" si="0"/>
-        <v>30.552475349948377</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>30.583491595597032</v>
       </c>
       <c r="P12">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.792672986864563</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>24.818300541430126</v>
       </c>
       <c r="Q12">
-        <f t="shared" ca="1" si="0"/>
-        <v>18.821036441752238</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>18.840688516037645</v>
       </c>
       <c r="R12">
-        <f t="shared" ca="1" si="0"/>
-        <v>12.66416261883097</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>12.677428536235173</v>
       </c>
       <c r="S12">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.3690967793202269</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6.3757498537111355</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -7647,75 +7647,75 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>94.619604373060994</v>
+        <v>94.627565158466439</v>
       </c>
       <c r="C13">
-        <f t="shared" ca="1" si="0"/>
-        <v>89.270584624262966</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>89.286126071450411</v>
       </c>
       <c r="D13">
-        <f t="shared" ca="1" si="0"/>
-        <v>83.979898023847312</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>84.00244563795593</v>
       </c>
       <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>78.766472894136626</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>78.795276421381828</v>
       </c>
       <c r="F13">
-        <f t="shared" ca="1" si="0"/>
-        <v>73.63894140657402</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>73.67309768675824</v>
       </c>
       <c r="G13">
-        <f t="shared" ca="1" si="0"/>
-        <v>68.594852165472361</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>68.633331653579262</v>
       </c>
       <c r="H13">
-        <f t="shared" ca="1" si="0"/>
-        <v>63.621185842363793</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>63.662862130939843</v>
       </c>
       <c r="I13">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.695845328393695</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>58.739526912374565</v>
       </c>
       <c r="J13">
-        <f t="shared" ca="1" si="0"/>
-        <v>53.789789609437086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>53.834253057687377</v>
       </c>
       <c r="K13">
-        <f t="shared" ca="1" si="0"/>
-        <v>48.869565474994289</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>48.91358911400178</v>
       </c>
       <c r="L13">
-        <f t="shared" ca="1" si="0"/>
-        <v>43.900097801930016</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>43.94249498246559</v>
       </c>
       <c r="M13">
-        <f t="shared" ca="1" si="0"/>
-        <v>38.847678871010856</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>38.887329882859767</v>
       </c>
       <c r="N13">
-        <f t="shared" ca="1" si="0"/>
-        <v>33.683119316811094</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>33.71900104316363</v>
       </c>
       <c r="O13">
-        <f t="shared" ca="1" si="0"/>
-        <v>28.384970761850859</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>28.416183224989812</v>
       </c>
       <c r="P13">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.942599419621324</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>22.968388462423455</v>
       </c>
       <c r="Q13">
-        <f t="shared" ca="1" si="0"/>
-        <v>17.358700657160391</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>17.378476127750179</v>
       </c>
       <c r="R13">
-        <f t="shared" ca="1" si="0"/>
-        <v>11.650657219087133</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>11.664006173870046</v>
       </c>
       <c r="S13">
-        <f t="shared" ca="1" si="0"/>
-        <v>5.8500724617992574</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5.8567670685475033</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -7723,80 +7723,80 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>94.150066250985418</v>
+        <v>94.157954091983783</v>
       </c>
       <c r="C14">
-        <f t="shared" ca="1" si="0"/>
-        <v>88.349616183108495</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88.365014834907896</v>
       </c>
       <c r="D14">
-        <f t="shared" ca="1" si="0"/>
-        <v>82.6416997938679</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>82.664039614768114</v>
       </c>
       <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>77.057917032345514</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>77.086454250538665</v>
       </c>
       <c r="F14">
-        <f t="shared" ca="1" si="0"/>
-        <v>71.615647535487014</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>71.649486932153522</v>
       </c>
       <c r="G14">
-        <f t="shared" ca="1" si="0"/>
-        <v>66.3175839440663</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>66.355705168337948</v>
       </c>
       <c r="H14">
-        <f t="shared" ca="1" si="0"/>
-        <v>61.153090198390423</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>61.194377048443329</v>
       </c>
       <c r="I14">
-        <f t="shared" ca="1" si="0"/>
-        <v>56.100716160601792</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>56.14398807666349</v>
       </c>
       <c r="J14">
-        <f t="shared" ca="1" si="0"/>
-        <v>51.131271263947369</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>51.175316203327235</v>
       </c>
       <c r="K14">
-        <f t="shared" ca="1" si="0"/>
-        <v>46.211047178487057</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46.254654985605569</v>
       </c>
       <c r="L14">
-        <f t="shared" ca="1" si="0"/>
-        <v>41.304968777082827</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>41.346964128341604</v>
       </c>
       <c r="M14">
-        <f t="shared" ca="1" si="0"/>
-        <v>36.379583452116805</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>36.418857450883522</v>
       </c>
       <c r="N14">
-        <f t="shared" ca="1" si="0"/>
-        <v>31.405851383501755</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>31.441390907609158</v>
       </c>
       <c r="O14">
-        <f t="shared" ca="1" si="0"/>
-        <v>26.36167721634077</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>26.392591180607056</v>
       </c>
       <c r="P14">
-        <f t="shared" ca="1" si="0"/>
-        <v>21.234043890101219</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>21.259585678693412</v>
       </c>
       <c r="Q14">
-        <f t="shared" ca="1" si="0"/>
-        <v>16.020502731539128</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>16.040088176649263</v>
       </c>
       <c r="R14">
-        <f t="shared" ca="1" si="0"/>
-        <v>10.72968901758081</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>10.742909447062479</v>
       </c>
       <c r="S14">
-        <f t="shared" ca="1" si="0"/>
-        <v>5.380534477445007</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5.3871645183675199</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -7804,80 +7804,80 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>93.631039626315726</v>
+        <v>93.638731554620861</v>
       </c>
       <c r="C15">
-        <f t="shared" ca="1" si="0"/>
-        <v>87.336106267284634</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>87.351122088530843</v>
       </c>
       <c r="D15">
-        <f t="shared" ca="1" si="0"/>
-        <v>81.179357440510643</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>81.201141271119269</v>
       </c>
       <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>75.207835052827136</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>75.235661221139281</v>
       </c>
       <c r="F15">
-        <f t="shared" ca="1" si="0"/>
-        <v>69.448132947276378</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>69.481128151386159</v>
       </c>
       <c r="G15">
-        <f t="shared" ca="1" si="0"/>
-        <v>63.906729549929231</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>63.943898553758324</v>
       </c>
       <c r="H15">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.572857479138797</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>58.613111694145886</v>
       </c>
       <c r="I15">
-        <f t="shared" ca="1" si="0"/>
-        <v>53.422639936803307</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>53.464828151150634</v>
       </c>
       <c r="J15">
-        <f t="shared" ca="1" si="0"/>
-        <v>48.423514142117199</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>48.466454586281486</v>
       </c>
       <c r="K15">
-        <f t="shared" ca="1" si="0"/>
-        <v>43.538365670429023</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>43.580878553632544</v>
       </c>
       <c r="L15">
-        <f t="shared" ca="1" si="0"/>
-        <v>38.729130051574032</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>38.770069672227194</v>
       </c>
       <c r="M15">
-        <f t="shared" ca="1" si="0"/>
-        <v>33.959819487093036</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>33.998105017021018</v>
       </c>
       <c r="N15">
-        <f t="shared" ca="1" si="0"/>
-        <v>29.199011979183929</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>29.233656048706607</v>
       </c>
       <c r="O15">
-        <f t="shared" ca="1" si="0"/>
-        <v>24.421831311482535</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>24.451965581611852</v>
       </c>
       <c r="P15">
-        <f t="shared" ca="1" si="0"/>
-        <v>19.611386993839123</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>19.636283992151149</v>
       </c>
       <c r="Q15">
-        <f t="shared" ca="1" si="0"/>
-        <v>14.759570681249926</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14.778661296568698</v>
       </c>
       <c r="R15">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.8670576082883663</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9.8799437815243198</v>
       </c>
       <c r="S15">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.9423750952077627</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4.9488374033377207</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -7885,80 +7885,80 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>93.037981318081336</v>
+        <v>93.045359561193791</v>
       </c>
       <c r="C16">
-        <f t="shared" ca="1" si="0"/>
-        <v>86.184404278337681</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>86.198807397180147</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.531778501080581</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>79.552672920508158</v>
       </c>
       <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>73.145920368849261</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>73.172609664823597</v>
       </c>
       <c r="F16">
-        <f t="shared" ca="1" si="0"/>
-        <v>67.062305338542743</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>67.093951527975449</v>
       </c>
       <c r="G16">
-        <f t="shared" ca="1" si="0"/>
-        <v>61.288328055243653</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>61.323976276625793</v>
       </c>
       <c r="H16">
-        <f t="shared" ca="1" si="0"/>
-        <v>55.808953454529444</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>55.847559410158155</v>
       </c>
       <c r="I16">
-        <f t="shared" ca="1" si="0"/>
-        <v>50.593454661660466</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>50.633914110858463</v>
       </c>
       <c r="J16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45.601762347003756</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45.642941870765036</v>
       </c>
       <c r="K16">
-        <f t="shared" ca="1" si="0"/>
-        <v>40.789754383846201</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>40.830522589991588</v>
       </c>
       <c r="L16">
-        <f t="shared" ca="1" si="0"/>
-        <v>36.113350220184039</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>36.152608529254834</v>
       </c>
       <c r="M16">
-        <f t="shared" ca="1" si="0"/>
-        <v>31.531537704450173</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>31.5682498542599</v>
       </c>
       <c r="N16">
-        <f t="shared" ca="1" si="0"/>
-        <v>27.008532636464057</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>27.041752070203614</v>
       </c>
       <c r="O16">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.51523794058275</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>22.544132300698031</v>
       </c>
       <c r="P16">
-        <f t="shared" ca="1" si="0"/>
-        <v>18.030093217553794</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>18.053965254478374</v>
       </c>
       <c r="Q16">
-        <f t="shared" ca="1" si="0"/>
-        <v>13.539328949911173</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>13.557633268434934</v>
       </c>
       <c r="R16">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.0365917537026696</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9.0489469558411741</v>
       </c>
       <c r="S16">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.521907016268802</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4.5281029520821336</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -7966,80 +7966,80 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>92.336476921419603</v>
+        <v>92.343430728653914</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:C25" ca="1" si="3">AVERAGE(C16,B17,D17,C18)</f>
-        <v>84.831743854260139</v>
+        <f t="shared" ref="C17:C25" ca="1" si="5">AVERAGE(C16,B17,D17,C18)</f>
+        <v>84.845318123654181</v>
       </c>
       <c r="D17">
-        <f t="shared" ref="D17:D25" ca="1" si="4">AVERAGE(D16,C17,E17,D18)</f>
-        <v>77.617422270332355</v>
+        <f t="shared" ref="D17:D25" ca="1" si="6">AVERAGE(D16,C17,E17,D18)</f>
+        <v>77.637113795746345</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17:E25" ca="1" si="5">AVERAGE(E16,D17,F17,E18)</f>
-        <v>70.781750777373333</v>
+        <f t="shared" ref="E17:E25" ca="1" si="7">AVERAGE(E16,D17,F17,E18)</f>
+        <v>70.806902884067284</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F17:F25" ca="1" si="6">AVERAGE(F16,E17,G17,F18)</f>
-        <v>64.366826384100762</v>
+        <f t="shared" ref="F17:F25" ca="1" si="8">AVERAGE(F16,E17,G17,F18)</f>
+        <v>64.39664902647327</v>
       </c>
       <c r="G17">
-        <f t="shared" ref="G17:G25" ca="1" si="7">AVERAGE(G16,F17,H17,G18)</f>
-        <v>58.375308893052335</v>
+        <f t="shared" ref="G17:G25" ca="1" si="9">AVERAGE(G16,F17,H17,G18)</f>
+        <v>58.408901945271545</v>
       </c>
       <c r="H17">
-        <f t="shared" ref="H17:H25" ca="1" si="8">AVERAGE(H16,G17,I17,H18)</f>
-        <v>52.781157686696673</v>
+        <f t="shared" ref="H17:H25" ca="1" si="10">AVERAGE(H16,G17,I17,H18)</f>
+        <v>52.817536830281867</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I25" ca="1" si="9">AVERAGE(I16,H17,J17,I18)</f>
-        <v>47.540446474660691</v>
+        <f t="shared" ref="I17:I25" ca="1" si="11">AVERAGE(I16,H17,J17,I18)</f>
+        <v>47.578571010954626</v>
       </c>
       <c r="J17">
-        <f t="shared" ref="J17:J25" ca="1" si="10">AVERAGE(J16,I17,K17,J18)</f>
-        <v>42.600309724493016</v>
+        <f t="shared" ref="J17:J25" ca="1" si="12">AVERAGE(J16,I17,K17,J18)</f>
+        <v>42.639111575800939</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17:K25" ca="1" si="11">AVERAGE(K16,J17,L17,K18)</f>
-        <v>37.905523227012139</v>
+        <f t="shared" ref="K17:K25" ca="1" si="13">AVERAGE(K16,J17,L17,K18)</f>
+        <v>37.94393634274077</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17:L25" ca="1" si="12">AVERAGE(L16,K17,M17,L18)</f>
-        <v>33.402963502090749</v>
+        <f t="shared" ref="L17:L25" ca="1" si="14">AVERAGE(L16,K17,M17,L18)</f>
+        <v>33.439952859998769</v>
       </c>
       <c r="M17">
-        <f t="shared" ref="M17:M25" ca="1" si="13">AVERAGE(M16,L17,N17,M18)</f>
-        <v>29.044434462419744</v>
+        <f t="shared" ref="M17:M25" ca="1" si="15">AVERAGE(M16,L17,N17,M18)</f>
+        <v>29.07902385380936</v>
       </c>
       <c r="N17">
-        <f t="shared" ref="N17:N25" ca="1" si="14">AVERAGE(N16,M17,O17,N18)</f>
-        <v>24.788330490574623</v>
+        <f t="shared" ref="N17:N25" ca="1" si="16">AVERAGE(N16,M17,O17,N18)</f>
+        <v>24.819628304405768</v>
       </c>
       <c r="O17">
-        <f t="shared" ref="O17:O25" ca="1" si="15">AVERAGE(O16,N17,P17,O18)</f>
-        <v>20.600484049381258</v>
+        <f t="shared" ref="O17:O25" ca="1" si="17">AVERAGE(O16,N17,P17,O18)</f>
+        <v>20.627706324814028</v>
       </c>
       <c r="P17">
-        <f t="shared" ref="P17:P25" ca="1" si="16">AVERAGE(P16,O17,Q17,P18)</f>
-        <v>16.454410567555595</v>
+        <f t="shared" ref="P17:P25" ca="1" si="18">AVERAGE(P16,O17,Q17,P18)</f>
+        <v>16.476900666524006</v>
       </c>
       <c r="Q17">
-        <f t="shared" ref="Q17:Q25" ca="1" si="17">AVERAGE(Q16,P17,R17,Q18)</f>
-        <v>12.3310540404877</v>
+        <f t="shared" ref="Q17:Q25" ca="1" si="19">AVERAGE(Q16,P17,R17,Q18)</f>
+        <v>12.348298399020949</v>
       </c>
       <c r="R17">
-        <f t="shared" ref="R17:R25" ca="1" si="18">AVERAGE(R16,Q17,S17,R18)</f>
-        <v>8.2180697613670013</v>
+        <f t="shared" ref="R17:R25" ca="1" si="20">AVERAGE(R16,Q17,S17,R18)</f>
+        <v>8.2297093063309479</v>
       </c>
       <c r="S17">
-        <f t="shared" ref="S17:S25" ca="1" si="19">AVERAGE(S16,R17,T17,S18)</f>
-        <v>4.1086600125915664</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4.1144969738211872</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -8047,80 +8047,80 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>91.476178354857424</v>
+        <v>91.482605695897817</v>
       </c>
       <c r="C18">
+        <f t="shared" ca="1" si="5"/>
+        <v>83.201211556959748</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="6"/>
+        <v>75.342606829110395</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="7"/>
+        <v>68.020069297294924</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ca="1" si="8"/>
+        <v>61.275489942399801</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ca="1" si="9"/>
+        <v>55.095955295206018</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ca="1" si="10"/>
+        <v>49.433526732856159</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="11"/>
+        <v>44.222080123132649</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ca="1" si="12"/>
+        <v>39.389347969422836</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ca="1" si="13"/>
+        <v>34.864546543147029</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="14"/>
+        <v>30.582711523508301</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ca="1" si="15"/>
+        <v>26.486854213201916</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ca="1" si="16"/>
+        <v>22.528778167352591</v>
+      </c>
+      <c r="O18">
+        <f t="shared" ca="1" si="17"/>
+        <v>18.669099972200904</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ca="1" si="18"/>
+        <v>14.876782901118158</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" ca="1" si="19"/>
+        <v>11.128333874336185</v>
+      </c>
+      <c r="R18">
+        <f t="shared" ca="1" si="20"/>
+        <v>7.4067238385280634</v>
+      </c>
+      <c r="S18">
         <f t="shared" ca="1" si="3"/>
-        <v>83.188665247376278</v>
-      </c>
-      <c r="D18">
-        <f t="shared" ca="1" si="4"/>
-        <v>75.324406943902062</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="5"/>
-        <v>67.996823069732358</v>
-      </c>
-      <c r="F18">
-        <f t="shared" ca="1" si="6"/>
-        <v>61.247927840801758</v>
-      </c>
-      <c r="G18">
-        <f t="shared" ca="1" si="7"/>
-        <v>55.064909468939454</v>
-      </c>
-      <c r="H18">
-        <f t="shared" ca="1" si="8"/>
-        <v>49.399907063126896</v>
-      </c>
-      <c r="I18">
-        <f t="shared" ca="1" si="9"/>
-        <v>44.186848501854854</v>
-      </c>
-      <c r="J18">
-        <f t="shared" ca="1" si="10"/>
-        <v>39.353491488012494</v>
-      </c>
-      <c r="K18">
-        <f t="shared" ca="1" si="11"/>
-        <v>34.829050316075282</v>
-      </c>
-      <c r="L18">
-        <f t="shared" ca="1" si="12"/>
-        <v>30.548531894808594</v>
-      </c>
-      <c r="M18">
-        <f t="shared" ca="1" si="13"/>
-        <v>26.454893094504467</v>
-      </c>
-      <c r="N18">
-        <f t="shared" ca="1" si="14"/>
-        <v>22.499859231191678</v>
-      </c>
-      <c r="O18">
-        <f t="shared" ca="1" si="15"/>
-        <v>18.643947373496815</v>
-      </c>
-      <c r="P18">
-        <f t="shared" ca="1" si="16"/>
-        <v>14.856003123648092</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" ca="1" si="17"/>
-        <v>11.112401200047337</v>
-      </c>
-      <c r="R18">
-        <f t="shared" ca="1" si="18"/>
-        <v>7.3959698195496539</v>
-      </c>
-      <c r="S18">
-        <f t="shared" ca="1" si="19"/>
-        <v>3.6946621617180462</v>
+        <v>3.7000549804952882</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -8128,80 +8128,80 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="1"/>
-        <v>90.379567439124131</v>
+        <v>90.385376543601353</v>
       </c>
       <c r="C19">
+        <f t="shared" ca="1" si="5"/>
+        <v>81.133664982252824</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ca="1" si="6"/>
+        <v>72.511157535096515</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ca="1" si="7"/>
+        <v>64.654205474865336</v>
+      </c>
+      <c r="F19">
+        <f t="shared" ca="1" si="8"/>
+        <v>57.58804951369757</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ca="1" si="9"/>
+        <v>51.264537560371764</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ca="1" si="10"/>
+        <v>45.597080421276182</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ca="1" si="11"/>
+        <v>40.485372181218601</v>
+      </c>
+      <c r="J19">
+        <f t="shared" ca="1" si="12"/>
+        <v>35.830144330263138</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="13"/>
+        <v>31.540715511862359</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="14"/>
+        <v>27.538091740170358</v>
+      </c>
+      <c r="M19">
+        <f t="shared" ca="1" si="15"/>
+        <v>23.755613589752606</v>
+      </c>
+      <c r="N19">
+        <f t="shared" ca="1" si="16"/>
+        <v>20.138384720429592</v>
+      </c>
+      <c r="O19">
+        <f t="shared" ca="1" si="17"/>
+        <v>16.642159942349423</v>
+      </c>
+      <c r="P19">
+        <f t="shared" ca="1" si="18"/>
+        <v>13.232020741091858</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" ca="1" si="19"/>
+        <v>9.8809675723657797</v>
+      </c>
+      <c r="R19">
+        <f t="shared" ca="1" si="20"/>
+        <v>6.5684590003296215</v>
+      </c>
+      <c r="S19">
         <f t="shared" ca="1" si="3"/>
-        <v>81.122325705148029</v>
-      </c>
-      <c r="D19">
-        <f t="shared" ca="1" si="4"/>
-        <v>72.494708952822421</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="5"/>
-        <v>64.63319664571813</v>
-      </c>
-      <c r="F19">
-        <f t="shared" ca="1" si="6"/>
-        <v>57.563140845736086</v>
-      </c>
-      <c r="G19">
-        <f t="shared" ca="1" si="7"/>
-        <v>51.23648130734334</v>
-      </c>
-      <c r="H19">
-        <f t="shared" ca="1" si="8"/>
-        <v>45.566699018141207</v>
-      </c>
-      <c r="I19">
-        <f t="shared" ca="1" si="9"/>
-        <v>40.453534984473663</v>
-      </c>
-      <c r="J19">
-        <f t="shared" ca="1" si="10"/>
-        <v>35.797743380525979</v>
-      </c>
-      <c r="K19">
-        <f t="shared" ca="1" si="11"/>
-        <v>31.50864097427969</v>
-      </c>
-      <c r="L19">
-        <f t="shared" ca="1" si="12"/>
-        <v>27.507207698547163</v>
-      </c>
-      <c r="M19">
-        <f t="shared" ca="1" si="13"/>
-        <v>23.726734869935061</v>
-      </c>
-      <c r="N19">
-        <f t="shared" ca="1" si="14"/>
-        <v>20.112255395457339</v>
-      </c>
-      <c r="O19">
-        <f t="shared" ca="1" si="15"/>
-        <v>16.619434125547198</v>
-      </c>
-      <c r="P19">
-        <f t="shared" ca="1" si="16"/>
-        <v>13.213246204322679</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" ca="1" si="17"/>
-        <v>9.8665726372661968</v>
-      </c>
-      <c r="R19">
-        <f t="shared" ca="1" si="18"/>
-        <v>6.558743043943644</v>
-      </c>
-      <c r="S19">
-        <f t="shared" ca="1" si="19"/>
-        <v>3.2740178117592476</v>
+        <v>3.2788900144148667</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -8209,80 +8209,80 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="1"/>
-        <v>88.919762284427634</v>
+        <v>88.924872993575306</v>
       </c>
       <c r="C20">
+        <f t="shared" ca="1" si="5"/>
+        <v>78.436331545946402</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ca="1" si="6"/>
+        <v>68.913369677492469</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ca="1" si="7"/>
+        <v>60.496586671093581</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ca="1" si="8"/>
+        <v>53.156859441258469</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ca="1" si="9"/>
+        <v>46.775845016014472</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ca="1" si="10"/>
+        <v>41.203585814414645</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ca="1" si="11"/>
+        <v>36.290841624690138</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ca="1" si="12"/>
+        <v>31.903793787932415</v>
+      </c>
+      <c r="K20">
+        <f t="shared" ca="1" si="13"/>
+        <v>27.92876269145879</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="14"/>
+        <v>24.272076068083816</v>
+      </c>
+      <c r="M20">
+        <f t="shared" ca="1" si="15"/>
+        <v>20.857972836645772</v>
+      </c>
+      <c r="N20">
+        <f t="shared" ca="1" si="16"/>
+        <v>17.625965389352828</v>
+      </c>
+      <c r="O20">
+        <f t="shared" ca="1" si="17"/>
+        <v>14.528267125774327</v>
+      </c>
+      <c r="P20">
+        <f t="shared" ca="1" si="18"/>
+        <v>11.527480667272975</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" ca="1" si="19"/>
+        <v>8.5945555651937831</v>
+      </c>
+      <c r="R20">
+        <f t="shared" ca="1" si="20"/>
+        <v>5.7069540323798673</v>
+      </c>
+      <c r="S20">
         <f t="shared" ca="1" si="3"/>
-        <v>78.426355702368539</v>
-      </c>
-      <c r="D20">
-        <f t="shared" ca="1" si="4"/>
-        <v>68.898899163507025</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="5"/>
-        <v>60.478104726838986</v>
-      </c>
-      <c r="F20">
-        <f t="shared" ca="1" si="6"/>
-        <v>53.13494724517156</v>
-      </c>
-      <c r="G20">
-        <f t="shared" ca="1" si="7"/>
-        <v>46.751164505829571</v>
-      </c>
-      <c r="H20">
-        <f t="shared" ca="1" si="8"/>
-        <v>41.176860611171669</v>
-      </c>
-      <c r="I20">
-        <f t="shared" ca="1" si="9"/>
-        <v>36.262836558604008</v>
-      </c>
-      <c r="J20">
-        <f t="shared" ca="1" si="10"/>
-        <v>31.875293570391158</v>
-      </c>
-      <c r="K20">
-        <f t="shared" ca="1" si="11"/>
-        <v>27.900550310285261</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ca="1" si="12"/>
-        <v>24.244911500426163</v>
-      </c>
-      <c r="M20">
-        <f t="shared" ca="1" si="13"/>
-        <v>20.832572672931633</v>
-      </c>
-      <c r="N20">
-        <f t="shared" ca="1" si="14"/>
-        <v>17.602983941000073</v>
-      </c>
-      <c r="O20">
-        <f t="shared" ca="1" si="15"/>
-        <v>14.508279548242701</v>
-      </c>
-      <c r="P20">
-        <f t="shared" ca="1" si="16"/>
-        <v>11.510968569231121</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" ca="1" si="17"/>
-        <v>8.5818954959599001</v>
-      </c>
-      <c r="R20">
-        <f t="shared" ca="1" si="18"/>
-        <v>5.6984091463933275</v>
-      </c>
-      <c r="S20">
-        <f t="shared" ca="1" si="19"/>
-        <v>2.8426651598947483</v>
+        <v>2.846950067052306</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -8294,75 +8294,75 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="1"/>
-        <v>86.873123028675735</v>
+        <v>86.877467933630442</v>
       </c>
       <c r="C21">
+        <f t="shared" ca="1" si="5"/>
+        <v>74.772911800160045</v>
+      </c>
+      <c r="D21">
+        <f t="shared" ca="1" si="6"/>
+        <v>64.208722685493186</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ca="1" si="7"/>
+        <v>55.261079762938245</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ca="1" si="8"/>
+        <v>47.765997324326406</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ca="1" si="9"/>
+        <v>41.477339211917332</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ca="1" si="10"/>
+        <v>36.149449688412659</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ca="1" si="11"/>
+        <v>31.569451445101741</v>
+      </c>
+      <c r="J21">
+        <f t="shared" ca="1" si="12"/>
+        <v>27.56425869604125</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ca="1" si="13"/>
+        <v>23.997324901826929</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ca="1" si="14"/>
+        <v>20.76239442299681</v>
+      </c>
+      <c r="M21">
+        <f t="shared" ca="1" si="15"/>
+        <v>17.777240140896687</v>
+      </c>
+      <c r="N21">
+        <f t="shared" ca="1" si="16"/>
+        <v>14.978352770463001</v>
+      </c>
+      <c r="O21">
+        <f t="shared" ca="1" si="17"/>
+        <v>12.316712518433324</v>
+      </c>
+      <c r="P21">
+        <f t="shared" ca="1" si="18"/>
+        <v>9.75448128645046</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" ca="1" si="19"/>
+        <v>7.2623873953157103</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ca="1" si="20"/>
+        <v>4.8175926871401584</v>
+      </c>
+      <c r="S21">
         <f t="shared" ca="1" si="3"/>
-        <v>74.764430902070387</v>
-      </c>
-      <c r="D21">
-        <f t="shared" ca="1" si="4"/>
-        <v>64.196420897990293</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ca="1" si="5"/>
-        <v>55.245368066672498</v>
-      </c>
-      <c r="F21">
-        <f t="shared" ca="1" si="6"/>
-        <v>47.747369944956034</v>
-      </c>
-      <c r="G21">
-        <f t="shared" ca="1" si="7"/>
-        <v>41.456358999077601</v>
-      </c>
-      <c r="H21">
-        <f t="shared" ca="1" si="8"/>
-        <v>36.126731884883306</v>
-      </c>
-      <c r="I21">
-        <f t="shared" ca="1" si="9"/>
-        <v>31.545646271607641</v>
-      </c>
-      <c r="J21">
-        <f t="shared" ca="1" si="10"/>
-        <v>27.540033215263804</v>
-      </c>
-      <c r="K21">
-        <f t="shared" ca="1" si="11"/>
-        <v>23.973344652609217</v>
-      </c>
-      <c r="L21">
-        <f t="shared" ca="1" si="12"/>
-        <v>20.739305329825918</v>
-      </c>
-      <c r="M21">
-        <f t="shared" ca="1" si="13"/>
-        <v>17.755651202453752</v>
-      </c>
-      <c r="N21">
-        <f t="shared" ca="1" si="14"/>
-        <v>14.958820012990772</v>
-      </c>
-      <c r="O21">
-        <f t="shared" ca="1" si="15"/>
-        <v>12.299724664446876</v>
-      </c>
-      <c r="P21">
-        <f t="shared" ca="1" si="16"/>
-        <v>9.7404475374958857</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" ca="1" si="17"/>
-        <v>7.2516276606785492</v>
-      </c>
-      <c r="R21">
-        <f t="shared" ca="1" si="18"/>
-        <v>4.8103305111764803</v>
-      </c>
-      <c r="S21">
-        <f t="shared" ca="1" si="19"/>
-        <v>2.3982329326901097</v>
+        <v>2.4018745802527537</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -8370,80 +8370,80 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>83.808296442307721</v>
+        <v>83.81182178797377</v>
       </c>
       <c r="C22">
+        <f t="shared" ca="1" si="5"/>
+        <v>69.568701098568923</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ca="1" si="6"/>
+        <v>57.88696120066291</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ca="1" si="7"/>
+        <v>48.572317661450711</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ca="1" si="8"/>
+        <v>41.167910756212862</v>
+      </c>
+      <c r="G22">
+        <f t="shared" ca="1" si="9"/>
+        <v>35.217182736777204</v>
+      </c>
+      <c r="H22">
+        <f t="shared" ca="1" si="10"/>
+        <v>30.346483528735803</v>
+      </c>
+      <c r="I22">
+        <f t="shared" ca="1" si="11"/>
+        <v>26.27228677034865</v>
+      </c>
+      <c r="J22">
+        <f t="shared" ca="1" si="12"/>
+        <v>22.785492239320579</v>
+      </c>
+      <c r="K22">
+        <f t="shared" ca="1" si="13"/>
+        <v>19.732934492287185</v>
+      </c>
+      <c r="L22">
+        <f t="shared" ca="1" si="14"/>
+        <v>17.002035841598882</v>
+      </c>
+      <c r="M22">
+        <f t="shared" ca="1" si="15"/>
+        <v>14.509412062014773</v>
+      </c>
+      <c r="N22">
+        <f t="shared" ca="1" si="16"/>
+        <v>12.192758128259186</v>
+      </c>
+      <c r="O22">
+        <f t="shared" ca="1" si="17"/>
+        <v>10.005125872585168</v>
+      </c>
+      <c r="P22">
+        <f t="shared" ca="1" si="18"/>
+        <v>7.9108482943193712</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" ca="1" si="19"/>
+        <v>5.8825615534821543</v>
+      </c>
+      <c r="R22">
+        <f t="shared" ca="1" si="20"/>
+        <v>3.898940990524177</v>
+      </c>
+      <c r="S22">
         <f t="shared" ca="1" si="3"/>
-        <v>69.561820008715884</v>
-      </c>
-      <c r="D22">
-        <f t="shared" ca="1" si="4"/>
-        <v>57.876980143929707</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ca="1" si="5"/>
-        <v>48.559570208727777</v>
-      </c>
-      <c r="F22">
-        <f t="shared" ca="1" si="6"/>
-        <v>41.152798009256529</v>
-      </c>
-      <c r="G22">
-        <f t="shared" ca="1" si="7"/>
-        <v>35.200161452477673</v>
-      </c>
-      <c r="H22">
-        <f t="shared" ca="1" si="8"/>
-        <v>30.328052939457454</v>
-      </c>
-      <c r="I22">
-        <f t="shared" ca="1" si="9"/>
-        <v>26.252974446585604</v>
-      </c>
-      <c r="J22">
-        <f t="shared" ca="1" si="10"/>
-        <v>22.765839371490596</v>
-      </c>
-      <c r="K22">
-        <f t="shared" ca="1" si="11"/>
-        <v>19.71348099029953</v>
-      </c>
-      <c r="L22">
-        <f t="shared" ca="1" si="12"/>
-        <v>16.983305661840397</v>
-      </c>
-      <c r="M22">
-        <f t="shared" ca="1" si="13"/>
-        <v>14.491899169953959</v>
-      </c>
-      <c r="N22">
-        <f t="shared" ca="1" si="14"/>
-        <v>12.176913489910101</v>
-      </c>
-      <c r="O22">
-        <f t="shared" ca="1" si="15"/>
-        <v>9.9913458392771961</v>
-      </c>
-      <c r="P22">
-        <f t="shared" ca="1" si="16"/>
-        <v>7.8994647030774754</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" ca="1" si="17"/>
-        <v>5.8738338111480379</v>
-      </c>
-      <c r="R22">
-        <f t="shared" ca="1" si="18"/>
-        <v>3.8930503456059089</v>
-      </c>
-      <c r="S22">
-        <f t="shared" ca="1" si="19"/>
-        <v>1.9399354526230106</v>
+        <v>1.9428893178171331</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -8451,80 +8451,80 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>78.798240756345962</v>
+        <v>78.80090709481729</v>
       </c>
       <c r="C23">
+        <f t="shared" ca="1" si="5"/>
+        <v>61.802773745290516</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ca="1" si="6"/>
+        <v>49.197654078268037</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="7"/>
+        <v>39.972770421512934</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ca="1" si="8"/>
+        <v>33.115514148255158</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ca="1" si="9"/>
+        <v>27.876302152493437</v>
+      </c>
+      <c r="H23">
+        <f t="shared" ca="1" si="10"/>
+        <v>23.746275409555679</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ca="1" si="11"/>
+        <v>20.386956959764351</v>
+      </c>
+      <c r="J23">
+        <f t="shared" ca="1" si="12"/>
+        <v>17.571723816636453</v>
+      </c>
+      <c r="K23">
+        <f t="shared" ca="1" si="13"/>
+        <v>15.146138386695471</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ca="1" si="14"/>
+        <v>13.002694383316669</v>
+      </c>
+      <c r="M23">
+        <f t="shared" ca="1" si="15"/>
+        <v>11.064963342517782</v>
+      </c>
+      <c r="N23">
+        <f t="shared" ca="1" si="16"/>
+        <v>9.2775649382796495</v>
+      </c>
+      <c r="O23">
+        <f t="shared" ca="1" si="17"/>
+        <v>7.5996959665982819</v>
+      </c>
+      <c r="P23">
+        <f t="shared" ca="1" si="18"/>
+        <v>6.000835803610542</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ca="1" si="19"/>
+        <v>4.457789413219615</v>
+      </c>
+      <c r="R23">
+        <f t="shared" ca="1" si="20"/>
+        <v>2.9525542345548561</v>
+      </c>
+      <c r="S23">
         <f t="shared" ca="1" si="3"/>
-        <v>61.797569405438928</v>
-      </c>
-      <c r="D23">
-        <f t="shared" ca="1" si="4"/>
-        <v>49.190105263621582</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="5"/>
-        <v>39.963129499168083</v>
-      </c>
-      <c r="F23">
-        <f t="shared" ca="1" si="6"/>
-        <v>33.104084554076863</v>
-      </c>
-      <c r="G23">
-        <f t="shared" ca="1" si="7"/>
-        <v>27.863429399976358</v>
-      </c>
-      <c r="H23">
-        <f t="shared" ca="1" si="8"/>
-        <v>23.732337114038724</v>
-      </c>
-      <c r="I23">
-        <f t="shared" ca="1" si="9"/>
-        <v>20.372352140653962</v>
-      </c>
-      <c r="J23">
-        <f t="shared" ca="1" si="10"/>
-        <v>17.556861763152913</v>
-      </c>
-      <c r="K23">
-        <f t="shared" ca="1" si="11"/>
-        <v>15.131427388843214</v>
-      </c>
-      <c r="L23">
-        <f t="shared" ca="1" si="12"/>
-        <v>12.988530637788415</v>
-      </c>
-      <c r="M23">
-        <f t="shared" ca="1" si="13"/>
-        <v>11.051720341859664</v>
-      </c>
-      <c r="N23">
-        <f t="shared" ca="1" si="14"/>
-        <v>9.2655836400967466</v>
-      </c>
-      <c r="O23">
-        <f t="shared" ca="1" si="15"/>
-        <v>7.5892760176431544</v>
-      </c>
-      <c r="P23">
-        <f t="shared" ca="1" si="16"/>
-        <v>5.9922280616557595</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" ca="1" si="17"/>
-        <v>4.4511899686636749</v>
-      </c>
-      <c r="R23">
-        <f t="shared" ca="1" si="18"/>
-        <v>2.9481000853029871</v>
-      </c>
-      <c r="S23">
-        <f t="shared" ca="1" si="19"/>
-        <v>1.4684580733081234</v>
+        <v>1.4706915940000735</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -8532,80 +8532,80 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>69.587095732669326</v>
+        <v>69.588878315812366</v>
       </c>
       <c r="C24">
+        <f t="shared" ca="1" si="5"/>
+        <v>49.643588645362698</v>
+      </c>
+      <c r="D24">
+        <f t="shared" ca="1" si="6"/>
+        <v>37.12778562711766</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ca="1" si="7"/>
+        <v>29.005199493205296</v>
+      </c>
+      <c r="F24">
+        <f t="shared" ca="1" si="8"/>
+        <v>23.444617942601525</v>
+      </c>
+      <c r="G24">
+        <f t="shared" ca="1" si="9"/>
+        <v>19.425735326146981</v>
+      </c>
+      <c r="H24">
+        <f t="shared" ca="1" si="10"/>
+        <v>16.374826696403069</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ca="1" si="11"/>
+        <v>13.95699320656078</v>
+      </c>
+      <c r="J24">
+        <f t="shared" ca="1" si="12"/>
+        <v>11.967757894667162</v>
+      </c>
+      <c r="K24">
+        <f t="shared" ca="1" si="13"/>
+        <v>10.27666489423801</v>
+      </c>
+      <c r="L24">
+        <f t="shared" ca="1" si="14"/>
+        <v>8.7971321824336819</v>
+      </c>
+      <c r="M24">
+        <f t="shared" ca="1" si="15"/>
+        <v>7.4697157253874593</v>
+      </c>
+      <c r="N24">
+        <f t="shared" ca="1" si="16"/>
+        <v>6.2524295329074642</v>
+      </c>
+      <c r="O24">
+        <f t="shared" ca="1" si="17"/>
+        <v>5.1149082065813456</v>
+      </c>
+      <c r="P24">
+        <f t="shared" ca="1" si="18"/>
+        <v>4.034732524698831</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" ca="1" si="19"/>
+        <v>2.9950071959919797</v>
+      </c>
+      <c r="R24">
+        <f t="shared" ca="1" si="20"/>
+        <v>1.9826780389242262</v>
+      </c>
+      <c r="S24">
         <f t="shared" ca="1" si="3"/>
-        <v>49.640109312981565</v>
-      </c>
-      <c r="D24">
-        <f t="shared" ca="1" si="4"/>
-        <v>37.122738970404136</v>
-      </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="5"/>
-        <v>28.998754277681023</v>
-      </c>
-      <c r="F24">
-        <f t="shared" ca="1" si="6"/>
-        <v>23.436977072454638</v>
-      </c>
-      <c r="G24">
-        <f t="shared" ca="1" si="7"/>
-        <v>19.417129827375085</v>
-      </c>
-      <c r="H24">
-        <f t="shared" ca="1" si="8"/>
-        <v>16.365509042626861</v>
-      </c>
-      <c r="I24">
-        <f t="shared" ca="1" si="9"/>
-        <v>13.947230163616174</v>
-      </c>
-      <c r="J24">
-        <f t="shared" ca="1" si="10"/>
-        <v>11.957823075191346</v>
-      </c>
-      <c r="K24">
-        <f t="shared" ca="1" si="11"/>
-        <v>10.266831224084838</v>
-      </c>
-      <c r="L24">
-        <f t="shared" ca="1" si="12"/>
-        <v>8.7876644859023969</v>
-      </c>
-      <c r="M24">
-        <f t="shared" ca="1" si="13"/>
-        <v>7.4608636351362545</v>
-      </c>
-      <c r="N24">
-        <f t="shared" ca="1" si="14"/>
-        <v>6.2444209225513472</v>
-      </c>
-      <c r="O24">
-        <f t="shared" ca="1" si="15"/>
-        <v>5.107943329206373</v>
-      </c>
-      <c r="P24">
-        <f t="shared" ca="1" si="16"/>
-        <v>4.028979019126524</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" ca="1" si="17"/>
-        <v>2.9905960952649764</v>
-      </c>
-      <c r="R24">
-        <f t="shared" ca="1" si="18"/>
-        <v>1.9797008831906977</v>
-      </c>
-      <c r="S24">
-        <f t="shared" ca="1" si="19"/>
-        <v>0.98579644863688187</v>
+        <v>0.98728932855295437</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -8613,80 +8613,80 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="1"/>
-        <v>49.910031958259985</v>
+        <v>49.910920865011207</v>
       </c>
       <c r="C25">
+        <f t="shared" ca="1" si="5"/>
+        <v>30.054766739798566</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ca="1" si="6"/>
+        <v>20.66450170790992</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ca="1" si="7"/>
+        <v>15.475383216542127</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ca="1" si="8"/>
+        <v>12.23174711552635</v>
+      </c>
+      <c r="G25">
+        <f t="shared" ca="1" si="9"/>
+        <v>10.00689197373617</v>
+      </c>
+      <c r="H25">
+        <f t="shared" ca="1" si="10"/>
+        <v>8.3699821126830862</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ca="1" si="11"/>
+        <v>7.0981013680406084</v>
+      </c>
+      <c r="J25">
+        <f t="shared" ca="1" si="12"/>
+        <v>6.0653196984186755</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ca="1" si="13"/>
+        <v>5.1953100719810354</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ca="1" si="14"/>
+        <v>4.4391501931419297</v>
+      </c>
+      <c r="M25">
+        <f t="shared" ca="1" si="15"/>
+        <v>3.764059776687148</v>
+      </c>
+      <c r="N25">
+        <f t="shared" ca="1" si="16"/>
+        <v>3.1472837769331754</v>
+      </c>
+      <c r="O25">
+        <f t="shared" ca="1" si="17"/>
+        <v>2.5725679827470103</v>
+      </c>
+      <c r="P25">
+        <f t="shared" ca="1" si="18"/>
+        <v>2.0280156298778214</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" ca="1" si="19"/>
+        <v>1.5047126818478915</v>
+      </c>
+      <c r="R25">
+        <f t="shared" ca="1" si="20"/>
+        <v>0.99579460051490887</v>
+      </c>
+      <c r="S25">
         <f t="shared" ca="1" si="3"/>
-        <v>30.053031741751788</v>
-      </c>
-      <c r="D25">
-        <f t="shared" ca="1" si="4"/>
-        <v>20.661985175756151</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ca="1" si="5"/>
-        <v>15.472169327015765</v>
-      </c>
-      <c r="F25">
-        <f t="shared" ca="1" si="6"/>
-        <v>12.227937067999104</v>
-      </c>
-      <c r="G25">
-        <f t="shared" ca="1" si="7"/>
-        <v>10.002600987071055</v>
-      </c>
-      <c r="H25">
-        <f t="shared" ca="1" si="8"/>
-        <v>8.365336094738149</v>
-      </c>
-      <c r="I25">
-        <f t="shared" ca="1" si="9"/>
-        <v>7.093233345888736</v>
-      </c>
-      <c r="J25">
-        <f t="shared" ca="1" si="10"/>
-        <v>6.0603661047990114</v>
-      </c>
-      <c r="K25">
-        <f t="shared" ca="1" si="11"/>
-        <v>5.1904069886959228</v>
-      </c>
-      <c r="L25">
-        <f t="shared" ca="1" si="12"/>
-        <v>4.4344296545812103</v>
-      </c>
-      <c r="M25">
-        <f t="shared" ca="1" si="13"/>
-        <v>3.7596462360160139</v>
-      </c>
-      <c r="N25">
-        <f t="shared" ca="1" si="14"/>
-        <v>3.1432908334811116</v>
-      </c>
-      <c r="O25">
-        <f t="shared" ca="1" si="15"/>
-        <v>2.5690954617226129</v>
-      </c>
-      <c r="P25">
-        <f t="shared" ca="1" si="16"/>
-        <v>2.0251470948431254</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" ca="1" si="17"/>
-        <v>1.5025134467491084</v>
-      </c>
-      <c r="R25">
-        <f t="shared" ca="1" si="18"/>
-        <v>0.99431029199712817</v>
-      </c>
-      <c r="S25">
-        <f t="shared" ca="1" si="19"/>
-        <v>0.49502668515850251</v>
+        <v>0.49577098226696581</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -8846,75 +8846,75 @@
       </c>
       <c r="B2">
         <f ca="1">AVERAGE(B1,A2,C2,B3)</f>
-        <v>50.456859446151313</v>
+        <v>50.456764197585272</v>
       </c>
       <c r="C2">
         <f t="shared" ref="C2:S16" ca="1" si="0">AVERAGE(C1,B2,D2,C3)</f>
-        <v>31.144268646697213</v>
+        <v>31.144087185239417</v>
       </c>
       <c r="D2">
         <f t="shared" ca="1" si="0"/>
-        <v>22.291887646433864</v>
+        <v>22.291631406764335</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>17.629993135682618</v>
+        <v>17.629675196316992</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>14.895797389204184</v>
+        <v>14.895431694319274</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>13.153242952970206</v>
+        <v>13.152843616601507</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>11.960118701345277</v>
+        <v>11.959699465452246</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>11.080354862447127</v>
+        <v>11.079928724473955</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>10.37304435826502</v>
+        <v>10.372623332791683</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>9.7446972941567065</v>
+        <v>9.7442922568788113</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1266234970322895</v>
+        <v>9.1262440705920831</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4636301484337331</v>
+        <v>8.4632846091822813</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>7.708787609292842</v>
+        <v>7.708482809735262</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>6.8223128947817999</v>
+        <v>6.822054205049449</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>5.7738868364929612</v>
+        <v>5.7736781110322788</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>4.5478899231660002</v>
+        <v>4.5477334982621</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>3.1502715337069551</v>
+        <v>3.1501682593188409</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6141880787586909</v>
+        <v>1.6141373855523151</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8926,75 +8926,75 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:F18" ca="1" si="1">AVERAGE(B2,A3,C3,B4)</f>
-        <v>70.683146501104147</v>
+        <v>70.682969605101235</v>
       </c>
       <c r="C3">
         <f t="shared" ca="1" si="0"/>
-        <v>51.828289995930547</v>
+        <v>51.827953136607391</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>40.393238588558596</v>
+        <v>40.392763245500014</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>33.332226968570289</v>
+        <v>33.331637684183264</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>28.799885112853719</v>
+        <v>28.799207964357365</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>25.756982056144217</v>
+        <v>25.756243306633184</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
-        <v>23.606800437440675</v>
+        <v>23.606025520732157</v>
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>21.988179233298098</v>
+        <v>21.987392099650521</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
-        <v>20.667049623378141</v>
+        <v>20.66627234981263</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v>19.479049080168743</v>
+        <v>19.478301624130207</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>18.298099403036066</v>
+        <v>18.297399416306064</v>
       </c>
       <c r="M3">
         <f t="shared" ca="1" si="0"/>
-        <v>17.019048889384432</v>
+        <v>17.018411556400721</v>
       </c>
       <c r="N3">
         <f t="shared" ca="1" si="0"/>
-        <v>15.549154528007088</v>
+        <v>15.548592424708399</v>
       </c>
       <c r="O3">
         <f t="shared" ca="1" si="0"/>
-        <v>13.806532915348253</v>
+        <v>13.806055899429488</v>
       </c>
       <c r="P3">
         <f t="shared" ca="1" si="0"/>
-        <v>11.725309594094737</v>
+        <v>11.724924740816963</v>
       </c>
       <c r="Q3">
         <f t="shared" ca="1" si="0"/>
-        <v>9.2673760275937269</v>
+        <v>9.2670876226968435</v>
       </c>
       <c r="R3">
         <f t="shared" ca="1" si="0"/>
-        <v>6.4389925570143305</v>
+        <v>6.4388021534606796</v>
       </c>
       <c r="S3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3064747427656602</v>
+        <v>3.3063812828903156</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9006,75 +9006,75 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="1"/>
-        <v>80.447400174078865</v>
+        <v>80.447161086211608</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>65.092447421366714</v>
+        <v>65.091992510587829</v>
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>54.120471845272291</v>
+        <v>54.119830754443655</v>
       </c>
       <c r="E4">
         <f t="shared" ca="1" si="0"/>
-        <v>46.505697793464918</v>
+        <v>46.504904330556997</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="0"/>
-        <v>41.214429315716558</v>
+        <v>41.213519172291853</v>
       </c>
       <c r="G4">
         <f t="shared" ca="1" si="0"/>
-        <v>37.467887349118435</v>
+        <v>37.466896124839693</v>
       </c>
       <c r="H4">
         <f t="shared" ca="1" si="0"/>
-        <v>34.721805399418905</v>
+        <v>34.720767211190605</v>
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="0"/>
-        <v>32.598395089755371</v>
+        <v>32.597341803581259</v>
       </c>
       <c r="J4">
         <f t="shared" ca="1" si="0"/>
-        <v>30.827811490478741</v>
+        <v>30.826772342676083</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="0"/>
-        <v>29.206241100132431</v>
+        <v>29.205242473521409</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="0"/>
-        <v>27.56757518426452</v>
+        <v>27.566640414099489</v>
       </c>
       <c r="M4">
         <f t="shared" ca="1" si="0"/>
-        <v>25.765220599588179</v>
+        <v>25.764369775404546</v>
       </c>
       <c r="N4">
         <f t="shared" ca="1" si="0"/>
-        <v>23.662169657415212</v>
+        <v>23.661419433266754</v>
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="0"/>
-        <v>21.129288787386873</v>
+        <v>21.128652227141995</v>
       </c>
       <c r="P4">
         <f t="shared" ca="1" si="0"/>
-        <v>18.05339084735639</v>
+        <v>18.052877330108345</v>
       </c>
       <c r="Q4">
         <f t="shared" ca="1" si="0"/>
-        <v>14.357274894944094</v>
+        <v>14.356890098246987</v>
       </c>
       <c r="R4">
         <f t="shared" ca="1" si="0"/>
-        <v>10.031825478656911</v>
+        <v>10.031571448936331</v>
       </c>
       <c r="S4">
         <f t="shared" ca="1" si="0"/>
-        <v>5.1727102806627858</v>
+        <v>5.1725855925481286</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9086,75 +9086,75 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="1"/>
-        <v>86.013960449990762</v>
+        <v>86.013682229156558</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>73.973553693887169</v>
+        <v>73.973025065087285</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>64.490406269933644</v>
+        <v>64.489662931127981</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>57.355547156504322</v>
+        <v>57.354629711307126</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="0"/>
-        <v>52.08411741291463</v>
+        <v>52.083068269411022</v>
       </c>
       <c r="G5">
         <f t="shared" ca="1" si="0"/>
-        <v>48.17819407381181</v>
+        <v>48.177054809240637</v>
       </c>
       <c r="H5">
         <f t="shared" ca="1" si="0"/>
-        <v>45.213995691496031</v>
+        <v>45.212805395606757</v>
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="0"/>
-        <v>42.855640874620335</v>
+        <v>42.854435560805292</v>
       </c>
       <c r="J5">
         <f t="shared" ca="1" si="0"/>
-        <v>40.83942024884044</v>
+        <v>40.83823274378657</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.950395624942544</v>
+        <v>38.949255513177505</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="0"/>
-        <v>37.00061650728172</v>
+        <v>36.999549991163775</v>
       </c>
       <c r="M5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.811978011722196</v>
+        <v>34.811007697849291</v>
       </c>
       <c r="N5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.204918638849918</v>
+        <v>32.204063305810408</v>
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.994981845752374</v>
+        <v>28.994256245762013</v>
       </c>
       <c r="P5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.001627522289425</v>
+        <v>25.001042254226348</v>
       </c>
       <c r="Q5">
         <f t="shared" ca="1" si="0"/>
-        <v>20.076462515040781</v>
+        <v>20.076023991245663</v>
       </c>
       <c r="R5">
         <f t="shared" ca="1" si="0"/>
-        <v>14.158297434509802</v>
+        <v>14.158007951489068</v>
       </c>
       <c r="S5">
         <f t="shared" ca="1" si="0"/>
-        <v>7.3525317245539661</v>
+        <v>7.3523896383657092</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9166,75 +9166,75 @@
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="1"/>
-        <v>89.634835999829193</v>
+        <v>89.63454276532633</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>80.297318466040764</v>
+        <v>80.296762589475307</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>72.511944979137127</v>
+        <v>72.51116619367194</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="0"/>
-        <v>66.341839959904092</v>
+        <v>66.34088331413021</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="0"/>
-        <v>61.588157623120125</v>
+        <v>61.587069384801943</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="0"/>
-        <v>57.94662528301852</v>
+        <v>57.945449447102376</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="0"/>
-        <v>55.100187574256672</v>
+        <v>55.098964001187724</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="0"/>
-        <v>52.770597709878501</v>
+        <v>52.769362300243841</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="0"/>
-        <v>50.723682311176461</v>
+        <v>50.722467558484723</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="0"/>
-        <v>48.755161602912708</v>
+        <v>48.753996844235743</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="0"/>
-        <v>46.672384995150637</v>
+        <v>46.671296339526478</v>
       </c>
       <c r="M6">
         <f t="shared" ca="1" si="0"/>
-        <v>44.277037635870172</v>
+        <v>44.276047719016375</v>
       </c>
       <c r="N6">
         <f t="shared" ca="1" si="0"/>
-        <v>41.350442149826172</v>
+        <v>41.349569846361774</v>
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="0"/>
-        <v>37.64400702005068</v>
+        <v>37.643267195867836</v>
       </c>
       <c r="P6">
         <f t="shared" ca="1" si="0"/>
-        <v>32.881608099910643</v>
+        <v>32.881011449788197</v>
       </c>
       <c r="Q6">
         <f t="shared" ca="1" si="0"/>
-        <v>26.788602669001534</v>
+        <v>26.788155661019434</v>
       </c>
       <c r="R6">
         <f t="shared" ca="1" si="0"/>
-        <v>19.17234179343502</v>
+        <v>19.172046727408073</v>
       </c>
       <c r="S6">
         <f t="shared" ca="1" si="0"/>
-        <v>10.079109831512593</v>
+        <v>10.078965009425481</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9246,75 +9246,75 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>92.228011909717864</v>
+        <v>92.227726242672489</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>85.068855821649635</v>
+        <v>85.068316333814153</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>78.918107088841367</v>
+        <v>78.917355939952301</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="0"/>
-        <v>73.911583053378664</v>
+        <v>73.910667966737549</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="0"/>
-        <v>69.979907662675572</v>
+        <v>69.978876508561626</v>
       </c>
       <c r="G7">
         <f t="shared" ca="1" si="0"/>
-        <v>66.919813750168061</v>
+        <v>66.918709593176558</v>
       </c>
       <c r="H7">
         <f t="shared" ca="1" si="0"/>
-        <v>64.469380102550176</v>
+        <v>64.468238861795214</v>
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="0"/>
-        <v>62.402729222469603</v>
+        <v>62.401582080494954</v>
       </c>
       <c r="J7">
         <f t="shared" ca="1" si="0"/>
-        <v>60.529403171778888</v>
+        <v>60.528278345670145</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="0"/>
-        <v>58.674044672708334</v>
+        <v>58.672967965751845</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="0"/>
-        <v>56.656596123558188</v>
+        <v>56.655590803687772</v>
       </c>
       <c r="M7">
         <f t="shared" ca="1" si="0"/>
-        <v>54.27323055174714</v>
+        <v>54.272316992325955</v>
       </c>
       <c r="N7">
         <f t="shared" ca="1" si="0"/>
-        <v>51.275705863005861</v>
+        <v>51.274901164750744</v>
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="0"/>
-        <v>47.348913555253702</v>
+        <v>47.348231241557926</v>
       </c>
       <c r="P7">
         <f t="shared" ca="1" si="0"/>
-        <v>42.09213086794923</v>
+        <v>42.091580688038064</v>
       </c>
       <c r="Q7">
         <f t="shared" ca="1" si="0"/>
-        <v>35.023952625759563</v>
+        <v>35.023540475635002</v>
       </c>
       <c r="R7">
         <f t="shared" ca="1" si="0"/>
-        <v>25.663330327451991</v>
+        <v>25.663058287697851</v>
       </c>
       <c r="S7">
         <f t="shared" ca="1" si="0"/>
-        <v>13.791557188240112</v>
+        <v>13.791423671927991</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9326,75 +9326,75 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>94.208305341087708</v>
+        <v>94.208045871548535</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>88.83190753198835</v>
+        <v>88.831420563155064</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>84.17994409956259</v>
+        <v>84.179273265583745</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="0"/>
-        <v>80.406361090063541</v>
+        <v>80.405556104303912</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="0"/>
-        <v>77.499949551156746</v>
+        <v>77.499059089528174</v>
       </c>
       <c r="G8">
         <f t="shared" ca="1" si="0"/>
-        <v>75.283209774684991</v>
+        <v>75.282273555244657</v>
       </c>
       <c r="H8">
         <f t="shared" ca="1" si="0"/>
-        <v>73.454655793258326</v>
+        <v>73.453699772319197</v>
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="0"/>
-        <v>71.841403113559423</v>
+        <v>71.840448814268257</v>
       </c>
       <c r="J8">
         <f t="shared" ca="1" si="0"/>
-        <v>70.31702793725438</v>
+        <v>70.316095777946799</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="0"/>
-        <v>68.754896275579597</v>
+        <v>68.754005869411586</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="0"/>
-        <v>67.006612306178326</v>
+        <v>67.005781917144844</v>
       </c>
       <c r="M8">
         <f t="shared" ca="1" si="0"/>
-        <v>64.883482360766322</v>
+        <v>64.882728281847164</v>
       </c>
       <c r="N8">
         <f t="shared" ca="1" si="0"/>
-        <v>62.130150528094127</v>
+        <v>62.129486578755817</v>
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="0"/>
-        <v>58.383738746036855</v>
+        <v>58.383175917573801</v>
       </c>
       <c r="P8">
         <f t="shared" ca="1" si="0"/>
-        <v>53.113993346597503</v>
+        <v>53.113539585170173</v>
       </c>
       <c r="Q8">
         <f t="shared" ca="1" si="0"/>
-        <v>45.551707153106925</v>
+        <v>45.551367265783988</v>
       </c>
       <c r="R8">
         <f t="shared" ca="1" si="0"/>
-        <v>34.665446605151089</v>
+        <v>34.665222275819936</v>
       </c>
       <c r="S8">
         <f t="shared" ca="1" si="0"/>
-        <v>19.423781487477637</v>
+        <v>19.42367139058851</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9406,75 +9406,75 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>95.773257233592403</v>
+        <v>95.773036680365792</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>91.870456552630728</v>
+        <v>91.870046781672613</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>88.563314661100094</v>
+        <v>88.562760454922127</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="0"/>
-        <v>86.033870256323581</v>
+        <v>86.03322409536446</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="0"/>
-        <v>84.330216643831164</v>
+        <v>84.329530190000611</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="0"/>
-        <v>83.258315314765099</v>
+        <v>83.257625765952852</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="0"/>
-        <v>82.224525516119684</v>
+        <v>82.223837857966771</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="0"/>
-        <v>81.191096600516147</v>
+        <v>81.190417626310222</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="0"/>
-        <v>80.142309987720992</v>
+        <v>80.14165008243549</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="0"/>
-        <v>79.021806651519356</v>
+        <v>79.021177816801213</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="0"/>
-        <v>77.731388447444246</v>
+        <v>77.73080271363132</v>
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="0"/>
-        <v>76.123859195695104</v>
+        <v>76.123327639160721</v>
       </c>
       <c r="N9">
         <f t="shared" ca="1" si="0"/>
-        <v>73.977608798023482</v>
+        <v>73.977140950850412</v>
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="0"/>
-        <v>70.941842768290115</v>
+        <v>70.941446264810324</v>
       </c>
       <c r="P9">
         <f t="shared" ca="1" si="0"/>
-        <v>66.428354092143252</v>
+        <v>66.4280344692841</v>
       </c>
       <c r="Q9">
         <f t="shared" ca="1" si="0"/>
-        <v>59.403406117352624</v>
+        <v>59.403166726510335</v>
       </c>
       <c r="R9">
         <f t="shared" ca="1" si="0"/>
-        <v>48.022950151642782</v>
+        <v>48.022792159209089</v>
       </c>
       <c r="S9">
         <f t="shared" ca="1" si="0"/>
-        <v>29.238117152534315</v>
+        <v>29.238039614606031</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9486,75 +9486,75 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>97.014230056566987</v>
+        <v>97.014054068241336</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>94.313291415717316</v>
+        <v>94.312969428246419</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>92.168920129855948</v>
+        <v>92.168497677066483</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="0"/>
-        <v>90.835515612761014</v>
+        <v>90.835049632229854</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="0"/>
-        <v>90.528659279102243</v>
+        <v>90.528211809155664</v>
       </c>
       <c r="G10">
         <f t="shared" ca="1" si="0"/>
-        <v>91.19524140872889</v>
+        <v>91.194861460598148</v>
       </c>
       <c r="H10">
         <f t="shared" ca="1" si="0"/>
-        <v>90.993968132506922</v>
+        <v>90.993608267283633</v>
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="0"/>
-        <v>90.556083306964297</v>
+        <v>90.555733750569217</v>
       </c>
       <c r="J10">
         <f t="shared" ca="1" si="0"/>
-        <v>90.039246904981283</v>
+        <v>90.038909108682631</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v>89.458573761479386</v>
+        <v>89.458252601725434</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="0"/>
-        <v>88.773222322773748</v>
+        <v>88.772923481417564</v>
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="0"/>
-        <v>87.902909671166185</v>
+        <v>87.902638610313147</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="0"/>
-        <v>86.714541826196964</v>
+        <v>86.714303320674048</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="0"/>
-        <v>84.977635822663444</v>
+        <v>84.977433721532421</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="0"/>
-        <v>82.254148198229359</v>
+        <v>82.253985300645127</v>
       </c>
       <c r="Q10">
         <f t="shared" ca="1" si="0"/>
-        <v>77.610595010782504</v>
+        <v>77.610473011763858</v>
       </c>
       <c r="R10">
         <f t="shared" ca="1" si="0"/>
-        <v>68.784820533360545</v>
+        <v>68.784740019899857</v>
       </c>
       <c r="S10">
         <f t="shared" ca="1" si="0"/>
-        <v>49.505734421473718</v>
+        <v>49.505694908626474</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -9566,23 +9566,23 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>97.97034288368215</v>
+        <v>97.970210164352636</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>96.199517213172413</v>
+        <v>96.199279186004475</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>94.963510451070619</v>
+        <v>94.963211192866666</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="0"/>
-        <v>94.610565432726276</v>
+        <v>94.610264947331927</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="0"/>
-        <v>95.753625427065643</v>
+        <v>95.75340595379339</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -9633,23 +9633,23 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>98.667603215408903</v>
+        <v>98.667507403164365</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>97.55089458101358</v>
+        <v>97.55072595855161</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>96.875007157092455</v>
+        <v>96.874802961063182</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="0"/>
-        <v>96.889584276134997</v>
+        <v>96.889393010437345</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="0"/>
-        <v>97.875269274073332</v>
+        <v>97.875147058685826</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -9661,23 +9661,23 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>99.149160551240612</v>
+        <v>99.149093489752943</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
-        <v>98.461430541621056</v>
+        <v>98.461314283974019</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>98.096018620345006</v>
+        <v>98.095881682396765</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="0"/>
-        <v>98.19747978303468</v>
+        <v>98.197357074668133</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="0"/>
-        <v>98.857862757302243</v>
+        <v>98.857789270512484</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -9689,23 +9689,23 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>99.46759824152744</v>
+        <v>99.467552271873245</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
-        <v>99.049634832758684</v>
+        <v>99.049556005194532</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>98.850143532654087</v>
+        <v>98.850052409881499</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="0"/>
-        <v>98.946443838531309</v>
+        <v>98.946364335325725</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="0"/>
-        <v>99.358699067598309</v>
+        <v>99.358652948695934</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -9717,23 +9717,23 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>99.671590676709656</v>
+        <v>99.671559592545336</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
-        <v>99.419357962652597</v>
+        <v>99.419305055049193</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>99.308468040212716</v>
+        <v>99.308407616608804</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="0"/>
-        <v>99.379446805223495</v>
+        <v>99.379394908057208</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="0"/>
-        <v>99.630487812126916</v>
+        <v>99.630458188945482</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -9745,23 +9745,23 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>99.799401877007853</v>
+        <v>99.799381043258833</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
-        <v>99.647732294963433</v>
+        <v>99.647697005848002</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>99.584918091569378</v>
+        <v>99.584878093447202</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="0"/>
-        <v>99.632383532291271</v>
+        <v>99.632349491348762</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="0"/>
-        <v>99.78380416649307</v>
+        <v>99.78378489902876</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -9773,23 +9773,23 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>99.87828145729857</v>
+        <v>99.878267574641924</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>99.78724727476758</v>
+        <v>99.787223831636666</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="1"/>
-        <v>99.751084708455778</v>
+        <v>99.751058259983211</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="1"/>
-        <v>99.781362454864961</v>
+        <v>99.781340064861837</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="1"/>
-        <v>99.872344531321318</v>
+        <v>99.87233191582078</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -9801,23 +9801,23 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="1"/>
-        <v>99.926474636469123</v>
+        <v>99.926465423672141</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>99.871888014082145</v>
+        <v>99.871872486073485</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="1"/>
-        <v>99.850808519796942</v>
+        <v>99.850791049987109</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="1"/>
-        <v>99.869635335921572</v>
+        <v>99.869620592294567</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="1"/>
-        <v>99.924210985895996</v>
+        <v>99.924202699392509</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -9829,23 +9829,23 @@
       </c>
       <c r="B19">
         <f t="shared" ref="B19:F25" ca="1" si="2">AVERAGE(B18,A19,C19,B20)</f>
-        <v>99.955727726058754</v>
+        <v>99.955721633973099</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="2"/>
-        <v>99.9230198954873</v>
+        <v>99.923009638998025</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>99.910624381590793</v>
+        <v>99.910612861597116</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="2"/>
-        <v>99.922158259969734</v>
+        <v>99.922148554936769</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="2"/>
-        <v>99.954863736527329</v>
+        <v>99.954858289454734</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -9857,23 +9857,23 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="2"/>
-        <v>99.973415484353808</v>
+        <v>99.973411473222185</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="2"/>
-        <v>99.953838322933933</v>
+        <v>99.953831574348371</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>99.946509775111736</v>
+        <v>99.946502202466533</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="2"/>
-        <v>99.953508849514563</v>
+        <v>99.953502476400672</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="2"/>
-        <v>99.973085477743325</v>
+        <v>99.9730819034896</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -9885,23 +9885,23 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="2"/>
-        <v>99.984095306564967</v>
+        <v>99.984092684567273</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="2"/>
-        <v>99.972407392485152</v>
+        <v>99.972402982706726</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="2"/>
-        <v>99.96806684305858</v>
+        <v>99.968061897519974</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="2"/>
-        <v>99.972281404488967</v>
+        <v>99.972277244709716</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="2"/>
-        <v>99.983969180074112</v>
+        <v>99.983966848103037</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -9913,23 +9913,23 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="2"/>
-        <v>99.990557971545314</v>
+        <v>99.990556282340151</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="2"/>
-        <v>99.983628614798249</v>
+        <v>99.983625774391285</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="2"/>
-        <v>99.981068344735363</v>
+        <v>99.98106516019692</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="2"/>
-        <v>99.983580434553886</v>
+        <v>99.983577756815194</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="2"/>
-        <v>99.990509745024127</v>
+        <v>99.990508244212833</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -9941,23 +9941,23 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="2"/>
-        <v>99.994507724042549</v>
+        <v>99.994506670402046</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="2"/>
-        <v>99.990480443846337</v>
+        <v>99.990478672321331</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="2"/>
-        <v>99.988997197900602</v>
+        <v>99.988995212061212</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="2"/>
-        <v>99.990462047673731</v>
+        <v>99.990460378141336</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="2"/>
-        <v>99.99448930756553</v>
+        <v>99.994488371933102</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -9969,23 +9969,23 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="2"/>
-        <v>99.996992333953088</v>
+        <v>99.996991726946703</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="2"/>
-        <v>99.994788052963884</v>
+        <v>99.994787032430708</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="2"/>
-        <v>99.99397778148662</v>
+        <v>99.993976637585234</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="2"/>
-        <v>99.994781133374829</v>
+        <v>99.994780171755792</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="2"/>
-        <v>99.996985404256264</v>
+        <v>99.996984865378266</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -9997,23 +9997,23 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="2"/>
-        <v>99.998673478978887</v>
+        <v>99.998673204954059</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="2"/>
-        <v>99.997701553563218</v>
+        <v>99.997701092869505</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="2"/>
-        <v>99.997344650456128</v>
+        <v>99.997344134093254</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="2"/>
-        <v>99.997699239978914</v>
+        <v>99.997698805918304</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="2"/>
-        <v>99.998671161058795</v>
+        <v>99.998670917824143</v>
       </c>
       <c r="G25">
         <v>100</v>
